--- a/data/trending_integrated_20260918_14.xlsx
+++ b/data/trending_integrated_20260918_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27550</v>
+        <v>27200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+27.55%</t>
+          <t>'+25.93%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="F2" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G2" t="n">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>402411124000</v>
+        <v>410747827900</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>성호전자 주가 상승 흐름 및 매물 소화 과정. 강력한 프로그램 매수세와 미래 성장성에 대한 긍정적 전망.</t>
+          <t>성호전자의 가파른 주가 상승세와 미래 성장성 분석. 프로그램 매수세 유입 및 대장주로서의 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['프로그램 매수', '성장성', '매물 소화']</t>
+          <t>['성호전자', '주가', '성장성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18690</v>
+        <v>18580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.87%</t>
+          <t>'+15.19%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F3" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G3" t="n">
-        <v>2476</v>
+        <v>2507</v>
       </c>
       <c r="H3" t="n">
         <v>4.61</v>
@@ -702,7 +702,7 @@
         <v>4.88</v>
       </c>
       <c r="O3" t="n">
-        <v>798626229270</v>
+        <v>806440899410</v>
       </c>
       <c r="P3" t="n">
         <v>31500</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>텍사스 관련 긍정적 뉴스와 함께 18,000원 돌파 및 20,000원 돌파 기대감이 높으며, 숏커버링 발생 및 거래량 증가에 대한 분석 포함.</t>
+          <t>대한광통신의 급등세 및 2차 매물대 돌파에 대한 기대감. 미국 증시 관련 뉴스 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['텍사스', '숏커버링', '거래량 증가']</t>
+          <t>['대한광통신', '매물대', '공매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8120</v>
+        <v>8080</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.67%</t>
+          <t>'+15.10%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="H4" t="n">
         <v>0.6899999999999999</v>
@@ -794,7 +794,7 @@
         <v>0.59</v>
       </c>
       <c r="O4" t="n">
-        <v>152415252570</v>
+        <v>153076679970</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31100</v>
+        <v>31150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.89%</t>
+          <t>'+10.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G5" t="n">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="H5" t="n">
         <v>11.44</v>
@@ -886,7 +886,7 @@
         <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>196085985450</v>
+        <v>197776408725</v>
       </c>
       <c r="P5" t="n">
         <v>75900</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대한전선 주가 부진과 가온전선과의 비교. 저평가 해소 및 주가 상승에 대한 기대.</t>
+          <t>대한전선의 주가 부진과 가온전선과의 비교 분석. 저평가 해소 및 주가 상승에 대한 기대감이 나타남.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['저평가', '주가 상승', '가온전선']</t>
+          <t>['대한전선', '가온전선', '저평가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6430</v>
+        <v>12635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.35%</t>
+          <t>'+9.11%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.02</v>
+        <v>-0.67</v>
       </c>
       <c r="E6" t="n">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="F6" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="G6" t="n">
-        <v>195</v>
+        <v>732</v>
       </c>
       <c r="H6" t="n">
-        <v>2.85</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5880</v>
+        <v>11580</v>
       </c>
       <c r="K6" t="n">
-        <v>5950</v>
+        <v>12200</v>
       </c>
       <c r="L6" t="n">
-        <v>6920</v>
+        <v>13820</v>
       </c>
       <c r="M6" t="n">
-        <v>5840</v>
+        <v>12100</v>
       </c>
       <c r="N6" t="n">
-        <v>1.83</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>90560877010</v>
+        <v>124046985975</v>
       </c>
       <c r="P6" t="n">
-        <v>11760</v>
+        <v>21150</v>
       </c>
       <c r="Q6" t="n">
-        <v>1620</v>
+        <v>8140</v>
       </c>
       <c r="R6" t="n">
-        <v>733000</v>
+        <v>349000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>156000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>전환사채 발행 가능성에도 불구하고 박스권 돌파 및 외국인 순매수 1위 기록. 2026년 매출 1조원 및 영업익 600억원 예상.</t>
+          <t>파미셀의 주가 상승 기대감과 일부 손실 경험이 혼재된 의견. 외인/기관 동시 매수 언급 있으나 구체적 근거 부족.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['전환사채', '외국인 순매수', '매출 전망']</t>
+          <t>['외인', '기관', '매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12620</v>
+        <v>6370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.98%</t>
+          <t>'+8.33%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.67</v>
+        <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="F7" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="G7" t="n">
-        <v>714</v>
+        <v>202</v>
       </c>
       <c r="H7" t="n">
-        <v>8.029999999999999</v>
+        <v>2.85</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11580</v>
+        <v>5880</v>
       </c>
       <c r="K7" t="n">
-        <v>12200</v>
+        <v>5950</v>
       </c>
       <c r="L7" t="n">
-        <v>13820</v>
+        <v>6920</v>
       </c>
       <c r="M7" t="n">
-        <v>12100</v>
+        <v>5840</v>
       </c>
       <c r="N7" t="n">
-        <v>8.699999999999999</v>
+        <v>1.83</v>
       </c>
       <c r="O7" t="n">
-        <v>123677660755</v>
+        <v>91148414175</v>
       </c>
       <c r="P7" t="n">
-        <v>21150</v>
+        <v>11760</v>
       </c>
       <c r="Q7" t="n">
-        <v>8140</v>
+        <v>1620</v>
       </c>
       <c r="R7" t="n">
-        <v>349000</v>
+        <v>733000</v>
       </c>
       <c r="S7" t="n">
-        <v>156000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외인/기관 동시 매수 언급 있으나, 전반적으로 하락 및 손실 우려, 모더나 관련 기대감 있으나 불확실성 존재.</t>
+          <t>KBI메탈의 박스권 돌파 및 주가 상승 기대. 전환사채, 외국인 순매수 등 구체적 지표 언급. 변압기 관련 사업 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['모더나', '외인/기관', '손실 우려']</t>
+          <t>['KBI메탈', '박스권', '외국인']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13950</v>
+        <v>13890</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.48%</t>
+          <t>'+8.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F8" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G8" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="H8" t="n">
         <v>2.83</v>
@@ -1162,7 +1162,7 @@
         <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>143088884815</v>
+        <v>143992237865</v>
       </c>
       <c r="P8" t="n">
         <v>20300</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1848500</v>
+        <v>1847000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.93%</t>
+          <t>'+5.85%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G9" t="n">
-        <v>2367</v>
+        <v>2436</v>
       </c>
       <c r="H9" t="n">
         <v>50.1</v>
@@ -1254,7 +1254,7 @@
         <v>50.2</v>
       </c>
       <c r="O9" t="n">
-        <v>4089395972000</v>
+        <v>4202832468500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가 200만원 돌파 기대감 및 외인/기관 순매수 확인. 차분한 모아가는 전략과 목표가 상향 조정.</t>
+          <t>SK하이닉스의 주가 상승 전망 및 목표가 상향 언급. 개미 투자자 매도와 외인/기관 매수 동향 분석. 일본 금리 인상 영향 분석.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인 순매수', '목표가 상향', '모아가는 전략']</t>
+          <t>['SK하이닉스', '주가', '외인']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,70 +1299,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10760</v>
+        <v>13870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.98%</t>
+          <t>'+4.05%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.29</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="F10" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>180</v>
+        <v>602</v>
       </c>
       <c r="H10" t="n">
-        <v>18.13</v>
+        <v>4.92</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>10250</v>
+        <v>13330</v>
       </c>
       <c r="K10" t="n">
-        <v>10280</v>
+        <v>13600</v>
       </c>
       <c r="L10" t="n">
-        <v>11500</v>
+        <v>14050</v>
       </c>
       <c r="M10" t="n">
-        <v>10230</v>
+        <v>13210</v>
       </c>
       <c r="N10" t="n">
-        <v>18.42</v>
+        <v>4.99</v>
       </c>
       <c r="O10" t="n">
-        <v>195934204315</v>
+        <v>69470154940</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>30200</v>
       </c>
       <c r="Q10" t="n">
-        <v>1760</v>
+        <v>3540</v>
       </c>
       <c r="R10" t="n">
-        <v>33000</v>
+        <v>231000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>긍정적/부정적 의견 혼재, 주가 하락 가능성 언급. 뚜렷한 근거 없이 감정적 상승 기대.</t>
+          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['미국원전주', '매물대', '목표가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13910</v>
+        <v>10640</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.35%</t>
+          <t>'+3.80%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.29</v>
       </c>
       <c r="E11" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="G11" t="n">
-        <v>595</v>
+        <v>181</v>
       </c>
       <c r="H11" t="n">
-        <v>4.92</v>
+        <v>18.13</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13330</v>
+        <v>10250</v>
       </c>
       <c r="K11" t="n">
-        <v>13600</v>
+        <v>10280</v>
       </c>
       <c r="L11" t="n">
-        <v>14050</v>
+        <v>11500</v>
       </c>
       <c r="M11" t="n">
-        <v>13210</v>
+        <v>10230</v>
       </c>
       <c r="N11" t="n">
-        <v>4.99</v>
+        <v>18.42</v>
       </c>
       <c r="O11" t="n">
-        <v>68445313730</v>
+        <v>199749856545</v>
       </c>
       <c r="P11" t="n">
-        <v>30200</v>
+        <v>22450</v>
       </c>
       <c r="Q11" t="n">
-        <v>3540</v>
+        <v>1760</v>
       </c>
       <c r="R11" t="n">
-        <v>231000</v>
+        <v>33000</v>
       </c>
       <c r="S11" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
+          <t>긍정적/부정적 의견 혼재, 주가 하락 가능성 언급. 뚜렷한 근거 없이 감정적 상승 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['미국원전주', '매물대', '목표가']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11030</v>
+        <v>261000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.96%</t>
+          <t>'+3.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>99</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>444</v>
       </c>
       <c r="G12" t="n">
-        <v>211</v>
+        <v>1908</v>
       </c>
       <c r="H12" t="n">
-        <v>12.5</v>
+        <v>46.48</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10610</v>
+        <v>252500</v>
       </c>
       <c r="K12" t="n">
-        <v>10730</v>
+        <v>261000</v>
       </c>
       <c r="L12" t="n">
-        <v>12390</v>
+        <v>261500</v>
       </c>
       <c r="M12" t="n">
-        <v>10510</v>
+        <v>257500</v>
       </c>
       <c r="N12" t="n">
-        <v>12.6</v>
+        <v>46.52</v>
       </c>
       <c r="O12" t="n">
-        <v>116352419850</v>
+        <v>2324769989750</v>
       </c>
       <c r="P12" t="n">
-        <v>14350</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>465</v>
+        <v>78600</v>
       </c>
       <c r="R12" t="n">
-        <v>46000</v>
+        <v>-1310000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>717000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
+          <t>삼성전자에 대한 분석 없이 정치적 언급이 주를 이룸.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,51 +1555,51 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['호남 반도체', '기자회견', '국내 이익']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>260750</v>
+        <v>10960</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.27%</t>
+          <t>'+3.30%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>451</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>1937</v>
+        <v>213</v>
       </c>
       <c r="H13" t="n">
-        <v>46.48</v>
+        <v>12.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>252500</v>
+        <v>10610</v>
       </c>
       <c r="K13" t="n">
-        <v>261000</v>
+        <v>10730</v>
       </c>
       <c r="L13" t="n">
-        <v>261500</v>
+        <v>12390</v>
       </c>
       <c r="M13" t="n">
-        <v>257500</v>
+        <v>10510</v>
       </c>
       <c r="N13" t="n">
-        <v>46.52</v>
+        <v>12.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2267853359750</v>
+        <v>116943868545</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>14350</v>
       </c>
       <c r="Q13" t="n">
-        <v>78600</v>
+        <v>465</v>
       </c>
       <c r="R13" t="n">
-        <v>-1310000</v>
+        <v>46000</v>
       </c>
       <c r="S13" t="n">
-        <v>717000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 논쟁 및 기자회견에 대한 부정적 의견 표출. 주가 관련 분석이나 팩트 기반 내용은 부재.</t>
+          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,20 +1647,20 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치', '기자회견', '논쟁']</t>
+          <t>['호남 반도체', '기자회견', '국내 이익']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>109</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19020</v>
+        <v>18970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.87%</t>
+          <t>'+2.60%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.11</v>
       </c>
       <c r="E14" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F14" t="n">
         <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="H14" t="n">
         <v>10.74</v>
@@ -1714,7 +1714,7 @@
         <v>10.85</v>
       </c>
       <c r="O14" t="n">
-        <v>125516179310</v>
+        <v>127075826080</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대우건설 주가 상승을 막는다는 주장에 대한 대차해지 운동 동참 요구. 수주 발표 이후 주가 하락에 대한 의문 제기.</t>
+          <t>대우건설의 주가 상승 기대감과 함께 대차해지 운동 동참 호소가 반복됨. 수주 발표 후 주가 하락에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대차해지', '주주행동', '수주']</t>
+          <t>['대차해지', '수주', '주가']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17650</v>
+        <v>17600</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.32%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.27</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H15" t="n">
         <v>0.97</v>
@@ -1806,7 +1806,7 @@
         <v>0.7</v>
       </c>
       <c r="O15" t="n">
-        <v>83320914940</v>
+        <v>83847815190</v>
       </c>
       <c r="P15" t="n">
         <v>30550</v>
@@ -1851,307 +1851,307 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52200</v>
+        <v>4175</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.15%</t>
+          <t>'+1.95%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="E16" t="n">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="F16" t="n">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>456</v>
+        <v>204</v>
       </c>
       <c r="H16" t="n">
-        <v>38.54</v>
+        <v>0.73</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>51100</v>
+        <v>4095</v>
       </c>
       <c r="K16" t="n">
-        <v>51600</v>
+        <v>4200</v>
       </c>
       <c r="L16" t="n">
-        <v>55200</v>
+        <v>4400</v>
       </c>
       <c r="M16" t="n">
-        <v>51500</v>
+        <v>4095</v>
       </c>
       <c r="N16" t="n">
-        <v>38.62</v>
+        <v>0.87</v>
       </c>
       <c r="O16" t="n">
-        <v>225923835550</v>
+        <v>69590376203</v>
       </c>
       <c r="P16" t="n">
-        <v>67300</v>
+        <v>8100</v>
       </c>
       <c r="Q16" t="n">
-        <v>23150</v>
+        <v>592</v>
       </c>
       <c r="R16" t="n">
-        <v>442000</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>외인/기관 매수세 및 시장 관심 증가에 따른 긍정적 주가 상승 전망.</t>
+          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['외인기관', '시장관심']</t>
+          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4170</v>
+        <v>52000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.83%</t>
+          <t>'+1.76%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="E17" t="n">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="G17" t="n">
-        <v>203</v>
+        <v>471</v>
       </c>
       <c r="H17" t="n">
-        <v>0.73</v>
+        <v>38.54</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4095</v>
+        <v>51100</v>
       </c>
       <c r="K17" t="n">
-        <v>4200</v>
+        <v>51600</v>
       </c>
       <c r="L17" t="n">
-        <v>4400</v>
+        <v>55200</v>
       </c>
       <c r="M17" t="n">
-        <v>4095</v>
+        <v>51500</v>
       </c>
       <c r="N17" t="n">
-        <v>0.87</v>
+        <v>38.62</v>
       </c>
       <c r="O17" t="n">
-        <v>68499598718</v>
+        <v>229407198200</v>
       </c>
       <c r="P17" t="n">
-        <v>8100</v>
+        <v>67300</v>
       </c>
       <c r="Q17" t="n">
-        <v>592</v>
+        <v>23150</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>442000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
+          <t>삼성E&amp;A의 주가 상승 기대감과 외인/기관 매수세 언급. 세금 정책 관련 언급 있으나 주가와 직접적 연관성 부족.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
+          <t>['삼성E&amp;A', '외인', '기관']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13380</v>
+        <v>17920</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.15%</t>
+          <t>'-0.06%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="E18" t="n">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="F18" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G18" t="n">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13360</v>
+        <v>17930</v>
       </c>
       <c r="K18" t="n">
-        <v>13450</v>
+        <v>18400</v>
       </c>
       <c r="L18" t="n">
-        <v>14450</v>
+        <v>20400</v>
       </c>
       <c r="M18" t="n">
-        <v>13280</v>
+        <v>17260</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O18" t="n">
-        <v>41497288750</v>
+        <v>83091467385</v>
       </c>
       <c r="P18" t="n">
-        <v>19380</v>
+        <v>21100</v>
       </c>
       <c r="Q18" t="n">
-        <v>3200</v>
+        <v>9900</v>
       </c>
       <c r="R18" t="n">
-        <v>-78000</v>
+        <v>32000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 상승 및 호남 반도체 사업 재개 기대감과 동시에, 단기 급등 후 하락 가능성 및 매도 의견 상존.</t>
+          <t>인제니아테라퓨틱스의 단기적 매매 접근 권유와 락업 해제 관련 우려. 주포의 움직임 분석 및 목표가 제시.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['호남 반도체', '실적', '단기 급등']</t>
+          <t>['인제니아테라퓨틱스', '락업해제', '주포']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>85300</v>
+        <v>13350</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>273</v>
+        <v>109</v>
       </c>
       <c r="F19" t="n">
-        <v>149</v>
+        <v>71</v>
       </c>
       <c r="G19" t="n">
-        <v>1274</v>
+        <v>385</v>
       </c>
       <c r="H19" t="n">
-        <v>23.23</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,143 +2159,143 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>85400</v>
+        <v>13360</v>
       </c>
       <c r="K19" t="n">
-        <v>87300</v>
+        <v>13450</v>
       </c>
       <c r="L19" t="n">
-        <v>87800</v>
+        <v>14450</v>
       </c>
       <c r="M19" t="n">
-        <v>85100</v>
+        <v>13280</v>
       </c>
       <c r="N19" t="n">
-        <v>23.27</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>113546814500</v>
+        <v>41748723555</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>19380</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>3200</v>
       </c>
       <c r="R19" t="n">
-        <v>-447000</v>
+        <v>-78000</v>
       </c>
       <c r="S19" t="n">
-        <v>-82000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 원전주 급등에 따른 두산에너빌리티 주가 상승 기대. 대미 투자 관련 발표 가능성과 엔비디아 전력 동맹 뉴스.</t>
+          <t>실적 상승 및 호남 반도체 사업 재개 기대감과 동시에, 단기 급등 후 하락 가능성 및 매도 의견 상존.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전주', '대미 투자', '전력 동맹']</t>
+          <t>['호남 반도체', '실적', '단기 급등']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17580</v>
+        <v>85300</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-1.95%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.38</v>
+        <v>-0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>159</v>
+        <v>281</v>
       </c>
       <c r="F20" t="n">
-        <v>74</v>
+        <v>152</v>
       </c>
       <c r="G20" t="n">
-        <v>385</v>
+        <v>1287</v>
       </c>
       <c r="H20" t="n">
-        <v>0.98</v>
+        <v>23.23</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>17930</v>
+        <v>85400</v>
       </c>
       <c r="K20" t="n">
-        <v>18400</v>
+        <v>87300</v>
       </c>
       <c r="L20" t="n">
-        <v>20400</v>
+        <v>87800</v>
       </c>
       <c r="M20" t="n">
-        <v>17260</v>
+        <v>85100</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6</v>
+        <v>23.27</v>
       </c>
       <c r="O20" t="n">
-        <v>82062171110</v>
+        <v>117453086650</v>
       </c>
       <c r="P20" t="n">
-        <v>21100</v>
+        <v>139200</v>
       </c>
       <c r="Q20" t="n">
-        <v>9900</v>
+        <v>57000</v>
       </c>
       <c r="R20" t="n">
-        <v>32000</v>
+        <v>-447000</v>
       </c>
       <c r="S20" t="n">
-        <v>12000</v>
+        <v>-82000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>단기 트레이딩에 적합한 종목으로 평가되며, 락업 해제 물량 소화 및 주포의 움직임에 대한 분석이 존재함. 바이오 섹터의 대세장 가능성이 언급되나, 목표 주가에 대한 기대와 현재 주가의 괴리에 대한 의견이 교차함.</t>
+          <t>미국 원전주 급등에 따른 두산에너빌리티 주가 상승 기대. 대미 투자 관련 발표 가능성과 엔비디아 전력 동맹 뉴스.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['락업해제', '주포', '바이오']</t>
+          <t>['원전주', '대미 투자', '전력 동맹']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10130</v>
+        <v>10150</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-3.52%</t>
+          <t>'-3.33%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F21" t="n">
         <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="H21" t="n">
         <v>1.24</v>
@@ -2358,7 +2358,7 @@
         <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>33616171590</v>
+        <v>33897212840</v>
       </c>
       <c r="P21" t="n">
         <v>15960</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4175</v>
+        <v>4180</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.92%</t>
+          <t>'-9.82%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.4</v>
       </c>
       <c r="E22" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F22" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G22" t="n">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="H22" t="n">
         <v>0.55</v>
@@ -2450,7 +2450,7 @@
         <v>0.95</v>
       </c>
       <c r="O22" t="n">
-        <v>37296281754</v>
+        <v>37459317019</v>
       </c>
       <c r="P22" t="n">
         <v>6900</v>
@@ -2510,13 +2510,13 @@
         <v>-0.02</v>
       </c>
       <c r="E23" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H23" t="n">
         <v>3.69</v>

--- a/data/trending_integrated_20260918_14.xlsx
+++ b/data/trending_integrated_20260918_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27200</v>
+        <v>26750</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+25.93%</t>
+          <t>'+23.84%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F2" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G2" t="n">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>410747827900</v>
+        <v>419524899750</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -619,14 +619,14 @@
         <v>1030</v>
       </c>
       <c r="R2" t="n">
-        <v>-149000</v>
+        <v>-223000</v>
       </c>
       <c r="S2" t="n">
-        <v>136000</v>
+        <v>181000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>성호전자의 가파른 주가 상승세와 미래 성장성 분석. 프로그램 매수세 유입 및 대장주로서의 가능성 언급.</t>
+          <t>매물 소화 후 하이킥 기대감. 5~6만원대 재진입 신호 및 폭풍 매수 확인.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['성호전자', '주가', '성장성']</t>
+          <t>['매물소화', '폭풍매수', '미래 성장성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18580</v>
+        <v>18505</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.19%</t>
+          <t>'+14.72%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="F3" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G3" t="n">
-        <v>2507</v>
+        <v>2560</v>
       </c>
       <c r="H3" t="n">
         <v>4.61</v>
@@ -702,7 +702,7 @@
         <v>4.88</v>
       </c>
       <c r="O3" t="n">
-        <v>806440899410</v>
+        <v>818781307545</v>
       </c>
       <c r="P3" t="n">
         <v>31500</v>
@@ -711,10 +711,10 @@
         <v>1272</v>
       </c>
       <c r="R3" t="n">
-        <v>1339000</v>
+        <v>1369000</v>
       </c>
       <c r="S3" t="n">
-        <v>131000</v>
+        <v>147000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8080</v>
+        <v>8050</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.10%</t>
+          <t>'+14.67%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="H4" t="n">
         <v>0.6899999999999999</v>
@@ -794,7 +794,7 @@
         <v>0.59</v>
       </c>
       <c r="O4" t="n">
-        <v>153076679970</v>
+        <v>155403415525</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -803,7 +803,7 @@
         <v>1206</v>
       </c>
       <c r="R4" t="n">
-        <v>603000</v>
+        <v>627000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31150</v>
+        <v>31250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.07%</t>
+          <t>'+10.42%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F5" t="n">
         <v>68</v>
       </c>
       <c r="G5" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H5" t="n">
         <v>11.44</v>
@@ -886,7 +886,7 @@
         <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>197776408725</v>
+        <v>199748040950</v>
       </c>
       <c r="P5" t="n">
         <v>75900</v>
@@ -895,23 +895,23 @@
         <v>15000</v>
       </c>
       <c r="R5" t="n">
-        <v>254000</v>
+        <v>249000</v>
       </c>
       <c r="S5" t="n">
-        <v>35000</v>
+        <v>31000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대한전선의 주가 부진과 가온전선과의 비교 분석. 저평가 해소 및 주가 상승에 대한 기대감이 나타남.</t>
+          <t>가온전선과의 비교 속 저평가 해소 및 상승 기대. 36,000원 도달 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['대한전선', '가온전선', '저평가']</t>
+          <t>['저평가', '가온전선', '상승']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12635</v>
+        <v>6390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.11%</t>
+          <t>'+8.67%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.67</v>
+        <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="F6" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>732</v>
+        <v>203</v>
       </c>
       <c r="H6" t="n">
-        <v>8.029999999999999</v>
+        <v>2.85</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>11580</v>
+        <v>5880</v>
       </c>
       <c r="K6" t="n">
-        <v>12200</v>
+        <v>5950</v>
       </c>
       <c r="L6" t="n">
-        <v>13820</v>
+        <v>6920</v>
       </c>
       <c r="M6" t="n">
-        <v>12100</v>
+        <v>5840</v>
       </c>
       <c r="N6" t="n">
-        <v>8.699999999999999</v>
+        <v>1.83</v>
       </c>
       <c r="O6" t="n">
-        <v>124046985975</v>
+        <v>91404224895</v>
       </c>
       <c r="P6" t="n">
-        <v>21150</v>
+        <v>11760</v>
       </c>
       <c r="Q6" t="n">
-        <v>8140</v>
+        <v>1620</v>
       </c>
       <c r="R6" t="n">
-        <v>349000</v>
+        <v>728000</v>
       </c>
       <c r="S6" t="n">
-        <v>156000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>파미셀의 주가 상승 기대감과 일부 손실 경험이 혼재된 의견. 외인/기관 동시 매수 언급 있으나 구체적 근거 부족.</t>
+          <t>박스권 돌파 및 전환사채 이슈. 외국인 순매수 1위 및 6500원 반등 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외인', '기관', '매수']</t>
+          <t>['박스권 돌파', '외국인 순매수', '전환사채']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6370</v>
+        <v>12560</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.33%</t>
+          <t>'+8.46%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.02</v>
+        <v>-0.67</v>
       </c>
       <c r="E7" t="n">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="G7" t="n">
-        <v>202</v>
+        <v>748</v>
       </c>
       <c r="H7" t="n">
-        <v>2.85</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5880</v>
+        <v>11580</v>
       </c>
       <c r="K7" t="n">
-        <v>5950</v>
+        <v>12200</v>
       </c>
       <c r="L7" t="n">
-        <v>6920</v>
+        <v>13820</v>
       </c>
       <c r="M7" t="n">
-        <v>5840</v>
+        <v>12100</v>
       </c>
       <c r="N7" t="n">
-        <v>1.83</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>91148414175</v>
+        <v>124764563080</v>
       </c>
       <c r="P7" t="n">
-        <v>11760</v>
+        <v>21150</v>
       </c>
       <c r="Q7" t="n">
-        <v>1620</v>
+        <v>8140</v>
       </c>
       <c r="R7" t="n">
-        <v>733000</v>
+        <v>276000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>169000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>KBI메탈의 박스권 돌파 및 주가 상승 기대. 전환사채, 외국인 순매수 등 구체적 지표 언급. 변압기 관련 사업 언급.</t>
+          <t>서로 다른 의견 속 매도 후 셀그램 관련 뉴스 기대. 외인/기관 동시 매수 확인.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['KBI메탈', '박스권', '외국인']</t>
+          <t>['셀그램', '외인', '기관']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13890</v>
+        <v>13860</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.01%</t>
+          <t>'+7.78%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H8" t="n">
         <v>2.83</v>
@@ -1162,7 +1162,7 @@
         <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>143992237865</v>
+        <v>144717315340</v>
       </c>
       <c r="P8" t="n">
         <v>20300</v>
@@ -1171,7 +1171,7 @@
         <v>2885</v>
       </c>
       <c r="R8" t="n">
-        <v>110000</v>
+        <v>130000</v>
       </c>
       <c r="S8" t="n">
         <v>48000</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1847000</v>
+        <v>1851000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.85%</t>
+          <t>'+6.07%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G9" t="n">
-        <v>2436</v>
+        <v>2455</v>
       </c>
       <c r="H9" t="n">
         <v>50.1</v>
@@ -1254,7 +1254,7 @@
         <v>50.2</v>
       </c>
       <c r="O9" t="n">
-        <v>4202832468500</v>
+        <v>4347651510500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1263,14 +1263,14 @@
         <v>333000</v>
       </c>
       <c r="R9" t="n">
-        <v>416000</v>
+        <v>483000</v>
       </c>
       <c r="S9" t="n">
         <v>116000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스의 주가 상승 전망 및 목표가 상향 언급. 개미 투자자 매도와 외인/기관 매수 동향 분석. 일본 금리 인상 영향 분석.</t>
+          <t>연말 500만원 목표 및 쌍끌이 매수 확인. 자사주 체결 및 괴리율 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '주가', '외인']</t>
+          <t>['목표가', '쌍끌이 매수', '자사주']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H10" t="n">
         <v>4.92</v>
@@ -1346,7 +1346,7 @@
         <v>4.99</v>
       </c>
       <c r="O10" t="n">
-        <v>69470154940</v>
+        <v>70347148795</v>
       </c>
       <c r="P10" t="n">
         <v>30200</v>
@@ -1355,10 +1355,10 @@
         <v>3540</v>
       </c>
       <c r="R10" t="n">
-        <v>231000</v>
+        <v>298000</v>
       </c>
       <c r="S10" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10640</v>
+        <v>11010</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.80%</t>
+          <t>'+3.77%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.29</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="F11" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="H11" t="n">
-        <v>18.13</v>
+        <v>12.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10250</v>
+        <v>10610</v>
       </c>
       <c r="K11" t="n">
-        <v>10280</v>
+        <v>10730</v>
       </c>
       <c r="L11" t="n">
-        <v>11500</v>
+        <v>12390</v>
       </c>
       <c r="M11" t="n">
-        <v>10230</v>
+        <v>10510</v>
       </c>
       <c r="N11" t="n">
-        <v>18.42</v>
+        <v>12.6</v>
       </c>
       <c r="O11" t="n">
-        <v>199749856545</v>
+        <v>117526979260</v>
       </c>
       <c r="P11" t="n">
-        <v>22450</v>
+        <v>14350</v>
       </c>
       <c r="Q11" t="n">
-        <v>1760</v>
+        <v>465</v>
       </c>
       <c r="R11" t="n">
-        <v>33000</v>
+        <v>74000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>긍정적/부정적 의견 혼재, 주가 하락 가능성 언급. 뚜렷한 근거 없이 감정적 상승 기대.</t>
+          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['호남 반도체', '기자회견', '국내 이익']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>261000</v>
+        <v>10630</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.37%</t>
+          <t>'+3.71%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>-0.29</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>118</v>
       </c>
       <c r="F12" t="n">
-        <v>444</v>
+        <v>72</v>
       </c>
       <c r="G12" t="n">
-        <v>1908</v>
+        <v>191</v>
       </c>
       <c r="H12" t="n">
-        <v>46.48</v>
+        <v>18.13</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>252500</v>
+        <v>10250</v>
       </c>
       <c r="K12" t="n">
-        <v>261000</v>
+        <v>10280</v>
       </c>
       <c r="L12" t="n">
-        <v>261500</v>
+        <v>11500</v>
       </c>
       <c r="M12" t="n">
-        <v>257500</v>
+        <v>10230</v>
       </c>
       <c r="N12" t="n">
-        <v>46.52</v>
+        <v>18.42</v>
       </c>
       <c r="O12" t="n">
-        <v>2324769989750</v>
+        <v>202530794275</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q12" t="n">
-        <v>78600</v>
+        <v>1760</v>
       </c>
       <c r="R12" t="n">
-        <v>-1310000</v>
+        <v>-55000</v>
       </c>
       <c r="S12" t="n">
-        <v>717000</v>
+        <v>1000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>삼성전자에 대한 분석 없이 정치적 언급이 주를 이룸.</t>
+          <t>긍정적/부정적 의견 혼재, 주가 하락 가능성 언급. 뚜렷한 근거 없이 감정적 상승 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1559,47 +1559,47 @@
         </is>
       </c>
       <c r="X12" t="n">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10960</v>
+        <v>261750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.30%</t>
+          <t>'+3.66%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>444</v>
       </c>
       <c r="G13" t="n">
-        <v>213</v>
+        <v>1894</v>
       </c>
       <c r="H13" t="n">
-        <v>12.5</v>
+        <v>46.48</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10610</v>
+        <v>252500</v>
       </c>
       <c r="K13" t="n">
-        <v>10730</v>
+        <v>261000</v>
       </c>
       <c r="L13" t="n">
-        <v>12390</v>
+        <v>262000</v>
       </c>
       <c r="M13" t="n">
-        <v>10510</v>
+        <v>257500</v>
       </c>
       <c r="N13" t="n">
-        <v>12.6</v>
+        <v>46.52</v>
       </c>
       <c r="O13" t="n">
-        <v>116943868545</v>
+        <v>2446660525250</v>
       </c>
       <c r="P13" t="n">
-        <v>14350</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>465</v>
+        <v>78600</v>
       </c>
       <c r="R13" t="n">
-        <v>46000</v>
+        <v>-1533000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>874000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
+          <t>대통령 및 정치 관련 언급이 주를 이루며, 기자회견 내용에 대한 부정적 평가.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,20 +1647,20 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['호남 반도체', '기자회견', '국내 이익']</t>
+          <t>['기자회견', '정치', '검찰개혁']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18970</v>
+        <v>19000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.60%</t>
+          <t>'+2.76%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.11</v>
       </c>
       <c r="E14" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F14" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G14" t="n">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="H14" t="n">
         <v>10.74</v>
@@ -1714,7 +1714,7 @@
         <v>10.85</v>
       </c>
       <c r="O14" t="n">
-        <v>127075826080</v>
+        <v>128642986280</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1723,14 +1723,14 @@
         <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>365000</v>
+        <v>350000</v>
       </c>
       <c r="S14" t="n">
-        <v>134000</v>
+        <v>135000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대우건설의 주가 상승 기대감과 함께 대차해지 운동 동참 호소가 반복됨. 수주 발표 후 주가 하락에 대한 의문 제기.</t>
+          <t>미국 원전주 상승 및 중동 전쟁 이슈 속 대차 해지 운동 주장. 수주 발표 후 하락에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대차해지', '수주', '주가']</t>
+          <t>['원전주', '대차해지', '수주']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,123 +1759,123 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17600</v>
+        <v>52500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.03%</t>
+          <t>'+2.74%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="E15" t="n">
+        <v>177</v>
+      </c>
+      <c r="F15" t="n">
         <v>94</v>
       </c>
-      <c r="F15" t="n">
-        <v>54</v>
-      </c>
       <c r="G15" t="n">
-        <v>181</v>
+        <v>494</v>
       </c>
       <c r="H15" t="n">
-        <v>0.97</v>
+        <v>38.54</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17250</v>
+        <v>51100</v>
       </c>
       <c r="K15" t="n">
-        <v>17920</v>
+        <v>51600</v>
       </c>
       <c r="L15" t="n">
-        <v>18440</v>
+        <v>55200</v>
       </c>
       <c r="M15" t="n">
-        <v>17450</v>
+        <v>51500</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7</v>
+        <v>38.62</v>
       </c>
       <c r="O15" t="n">
-        <v>83847815190</v>
+        <v>239231079900</v>
       </c>
       <c r="P15" t="n">
-        <v>30550</v>
+        <v>67300</v>
       </c>
       <c r="Q15" t="n">
-        <v>6100</v>
+        <v>23150</v>
       </c>
       <c r="R15" t="n">
-        <v>-123000</v>
+        <v>447000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>252000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터 주식(아이온큐)의 급등에 따른 기대감이 형성되었으나, 국내 시장에서의 주가 변동성은 크며 양자컴퓨터, AI 반도체, 보안 관련주 내에서의 상대적 위치에 대한 논의가 있음. 공공기관 보안 이슈가 언급되나, 투자자 유입은 제한적이라는 의견도 존재.</t>
+          <t>삼성E&amp;A의 주가 상승 기대감과 외인/기관 매수세 언급. 세금 정책 관련 언급 있으나 주가와 직접적 연관성 부족.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '보안', 'AI 반도체']</t>
+          <t>['삼성E&amp;A', '외인', '기관']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4175</v>
+        <v>17560</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.95%</t>
+          <t>'+1.80%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.14</v>
+        <v>0.27</v>
       </c>
       <c r="E16" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G16" t="n">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H16" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4095</v>
+        <v>17250</v>
       </c>
       <c r="K16" t="n">
-        <v>4200</v>
+        <v>17920</v>
       </c>
       <c r="L16" t="n">
-        <v>4400</v>
+        <v>18440</v>
       </c>
       <c r="M16" t="n">
-        <v>4095</v>
+        <v>17450</v>
       </c>
       <c r="N16" t="n">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>69590376203</v>
+        <v>84538546555</v>
       </c>
       <c r="P16" t="n">
-        <v>8100</v>
+        <v>30550</v>
       </c>
       <c r="Q16" t="n">
-        <v>592</v>
+        <v>6100</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-97000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
+          <t>미국 양자컴퓨터 주식(아이온큐)의 급등에 따른 기대감이 형성되었으나, 국내 시장에서의 주가 변동성은 크며 양자컴퓨터, AI 반도체, 보안 관련주 내에서의 상대적 위치에 대한 논의가 있음. 공공기관 보안 이슈가 언급되나, 투자자 유입은 제한적이라는 의견도 존재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
+          <t>['양자컴퓨터', '보안', 'AI 반도체']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,222 +1936,222 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52000</v>
+        <v>4160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.76%</t>
+          <t>'+1.59%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="E17" t="n">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="F17" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="G17" t="n">
-        <v>471</v>
+        <v>207</v>
       </c>
       <c r="H17" t="n">
-        <v>38.54</v>
+        <v>0.73</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>51100</v>
+        <v>4095</v>
       </c>
       <c r="K17" t="n">
-        <v>51600</v>
+        <v>4200</v>
       </c>
       <c r="L17" t="n">
-        <v>55200</v>
+        <v>4400</v>
       </c>
       <c r="M17" t="n">
-        <v>51500</v>
+        <v>4095</v>
       </c>
       <c r="N17" t="n">
-        <v>38.62</v>
+        <v>0.87</v>
       </c>
       <c r="O17" t="n">
-        <v>229407198200</v>
+        <v>70640387036</v>
       </c>
       <c r="P17" t="n">
-        <v>67300</v>
+        <v>8100</v>
       </c>
       <c r="Q17" t="n">
-        <v>23150</v>
+        <v>592</v>
       </c>
       <c r="R17" t="n">
-        <v>442000</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>삼성E&amp;A의 주가 상승 기대감과 외인/기관 매수세 언급. 세금 정책 관련 언급 있으나 주가와 직접적 연관성 부족.</t>
+          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['삼성E&amp;A', '외인', '기관']</t>
+          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17920</v>
+        <v>13370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.06%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="F18" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G18" t="n">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="H18" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17930</v>
+        <v>13360</v>
       </c>
       <c r="K18" t="n">
-        <v>18400</v>
+        <v>13450</v>
       </c>
       <c r="L18" t="n">
-        <v>20400</v>
+        <v>14450</v>
       </c>
       <c r="M18" t="n">
-        <v>17260</v>
+        <v>13280</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>83091467385</v>
+        <v>41864271890</v>
       </c>
       <c r="P18" t="n">
-        <v>21100</v>
+        <v>19380</v>
       </c>
       <c r="Q18" t="n">
-        <v>9900</v>
+        <v>3200</v>
       </c>
       <c r="R18" t="n">
-        <v>32000</v>
+        <v>-88000</v>
       </c>
       <c r="S18" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스의 단기적 매매 접근 권유와 락업 해제 관련 우려. 주포의 움직임 분석 및 목표가 제시.</t>
+          <t>실적 상승 및 호남 반도체 사업 재개 기대감과 동시에, 단기 급등 후 하락 가능성 및 매도 의견 상존.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['인제니아테라퓨틱스', '락업해제', '주포']</t>
+          <t>['호남 반도체', '실적', '단기 급등']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13350</v>
+        <v>85200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>109</v>
+        <v>286</v>
       </c>
       <c r="F19" t="n">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="G19" t="n">
-        <v>385</v>
+        <v>1305</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>23.23</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,143 +2159,143 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>13360</v>
+        <v>85400</v>
       </c>
       <c r="K19" t="n">
-        <v>13450</v>
+        <v>87300</v>
       </c>
       <c r="L19" t="n">
-        <v>14450</v>
+        <v>87800</v>
       </c>
       <c r="M19" t="n">
-        <v>13280</v>
+        <v>85100</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>23.27</v>
       </c>
       <c r="O19" t="n">
-        <v>41748723555</v>
+        <v>121158467150</v>
       </c>
       <c r="P19" t="n">
-        <v>19380</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>3200</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-78000</v>
+        <v>-476000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-94000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>실적 상승 및 호남 반도체 사업 재개 기대감과 동시에, 단기 급등 후 하락 가능성 및 매도 의견 상존.</t>
+          <t>뉴욕 원전주 급등 및 미국 투자 관련 발표 가능성. 웨스팅하우스 관련 리스크 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['호남 반도체', '실적', '단기 급등']</t>
+          <t>['원전주', '미국 투자', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>85300</v>
+        <v>17800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'-0.73%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.04</v>
+        <v>0.38</v>
       </c>
       <c r="E20" t="n">
-        <v>281</v>
+        <v>169</v>
       </c>
       <c r="F20" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="G20" t="n">
-        <v>1287</v>
+        <v>401</v>
       </c>
       <c r="H20" t="n">
-        <v>23.23</v>
+        <v>0.98</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>85400</v>
+        <v>17930</v>
       </c>
       <c r="K20" t="n">
-        <v>87300</v>
+        <v>18400</v>
       </c>
       <c r="L20" t="n">
-        <v>87800</v>
+        <v>20400</v>
       </c>
       <c r="M20" t="n">
-        <v>85100</v>
+        <v>17260</v>
       </c>
       <c r="N20" t="n">
-        <v>23.27</v>
+        <v>0.6</v>
       </c>
       <c r="O20" t="n">
-        <v>117453086650</v>
+        <v>83778068960</v>
       </c>
       <c r="P20" t="n">
-        <v>139200</v>
+        <v>21100</v>
       </c>
       <c r="Q20" t="n">
-        <v>57000</v>
+        <v>9900</v>
       </c>
       <c r="R20" t="n">
-        <v>-447000</v>
+        <v>43000</v>
       </c>
       <c r="S20" t="n">
-        <v>-82000</v>
+        <v>-1000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 원전주 급등에 따른 두산에너빌리티 주가 상승 기대. 대미 투자 관련 발표 가능성과 엔비디아 전력 동맹 뉴스.</t>
+          <t>단타 위주 매매 및 락업 해제 관련 언급. 주포의 움직임 및 엑시트 물량 소화 중.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전주', '대미 투자', '전력 동맹']</t>
+          <t>['단타', '락업해제', '주포']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10150</v>
+        <v>10110</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-3.33%</t>
+          <t>'-3.71%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F21" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G21" t="n">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="H21" t="n">
         <v>1.24</v>
@@ -2358,7 +2358,7 @@
         <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>33897212840</v>
+        <v>34409387165</v>
       </c>
       <c r="P21" t="n">
         <v>15960</v>
@@ -2367,7 +2367,7 @@
         <v>3500</v>
       </c>
       <c r="R21" t="n">
-        <v>-117000</v>
+        <v>-114000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4180</v>
+        <v>4120</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.82%</t>
+          <t>'-11.11%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.4</v>
       </c>
       <c r="E22" t="n">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F22" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G22" t="n">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="H22" t="n">
         <v>0.55</v>
@@ -2444,13 +2444,13 @@
         <v>4535</v>
       </c>
       <c r="M22" t="n">
-        <v>4125</v>
+        <v>4065</v>
       </c>
       <c r="N22" t="n">
         <v>0.95</v>
       </c>
       <c r="O22" t="n">
-        <v>37459317019</v>
+        <v>39407894761</v>
       </c>
       <c r="P22" t="n">
         <v>6900</v>
@@ -2459,7 +2459,7 @@
         <v>1738</v>
       </c>
       <c r="R22" t="n">
-        <v>-93000</v>
+        <v>-108000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2510,13 +2510,13 @@
         <v>-0.02</v>
       </c>
       <c r="E23" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F23" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H23" t="n">
         <v>3.69</v>

--- a/data/trending_integrated_20260918_14.xlsx
+++ b/data/trending_integrated_20260918_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26750</v>
+        <v>26250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.84%</t>
+          <t>'+39.04%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F2" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G2" t="n">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>21600</v>
+        <v>18880</v>
       </c>
       <c r="K2" t="n">
-        <v>22250</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>28050</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>21700</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>419524899750</v>
+        <v>435261000000</v>
       </c>
       <c r="P2" t="n">
-        <v>59600</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1030</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-223000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>181000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>매물 소화 후 하이킥 기대감. 5~6만원대 재진입 신호 및 폭풍 매수 확인.</t>
+          <t>강력한 매수세와 함께 5~6만원대 재진입 신호 및 미래 SK하이닉스와 같은 성장성 언급. 45% 수익 달성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['매물소화', '폭풍매수', '미래 성장성']</t>
+          <t>['매수세', '성장성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18505</v>
+        <v>17930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.72%</t>
+          <t>'+16.73%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.27</v>
+        <v>0.38</v>
       </c>
       <c r="E3" t="n">
-        <v>454</v>
+        <v>173</v>
       </c>
       <c r="F3" t="n">
-        <v>271</v>
+        <v>75</v>
       </c>
       <c r="G3" t="n">
-        <v>2560</v>
+        <v>400</v>
       </c>
       <c r="H3" t="n">
-        <v>4.61</v>
+        <v>0.98</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16130</v>
+        <v>15360</v>
       </c>
       <c r="K3" t="n">
-        <v>16360</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>18990</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>16170</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.88</v>
+        <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>818781307545</v>
+        <v>84670000000</v>
       </c>
       <c r="P3" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1369000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>147000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>대한광통신의 급등세 및 2차 매물대 돌파에 대한 기대감. 미국 증시 관련 뉴스 및 공매도 관련 언급.</t>
+          <t>단타 위주 매매 및 락업 해제 관련 언급. 주포의 움직임 및 엑시트 물량 소화 중.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['대한광통신', '매물대', '공매도']</t>
+          <t>['단타', '락업해제', '주포']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8050</v>
+        <v>6470</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.67%</t>
+          <t>'+15.12%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>1.02</v>
       </c>
       <c r="E4" t="n">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>406</v>
+        <v>207</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.85</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7020</v>
+        <v>5620</v>
       </c>
       <c r="K4" t="n">
-        <v>7180</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8890</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>7150</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.59</v>
+        <v>1.83</v>
       </c>
       <c r="O4" t="n">
-        <v>155403415525</v>
+        <v>92275000000</v>
       </c>
       <c r="P4" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>627000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>공시 내용 기반 월요일 10,000원 돌파 기대감 있으나, 일부에서는 급락 및 폭포수 현상 우려.</t>
+          <t>26년말 매출액 및 영업이익 예상치 기반 긍정적 전망. 전환사채 발행에도 상한가 기대감 및 외국인 대규모 매수세 분석.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공시', '외국인 매수', '급락 우려']</t>
+          <t>['매출액', '영업이익', '외국인 매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,95 +827,95 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31250</v>
+        <v>18450</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.42%</t>
+          <t>'+13.68%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>-0.27</v>
       </c>
       <c r="E5" t="n">
-        <v>139</v>
+        <v>458</v>
       </c>
       <c r="F5" t="n">
-        <v>68</v>
+        <v>273</v>
       </c>
       <c r="G5" t="n">
-        <v>230</v>
+        <v>2590</v>
       </c>
       <c r="H5" t="n">
-        <v>11.44</v>
+        <v>4.61</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>28300</v>
+        <v>16230</v>
       </c>
       <c r="K5" t="n">
-        <v>28850</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>32050</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>28550</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>11.46</v>
+        <v>4.88</v>
       </c>
       <c r="O5" t="n">
-        <v>199748040950</v>
+        <v>828470000000</v>
       </c>
       <c r="P5" t="n">
-        <v>75900</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>249000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 속 저평가 해소 및 상승 기대. 36,000원 도달 가능성 언급.</t>
+          <t>대한광통신의 급등세 및 2차 매물대 돌파에 대한 기대감. 미국 증시 관련 뉴스 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['저평가', '가온전선', '상승']</t>
+          <t>['대한광통신', '매물대', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,86 +924,86 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6390</v>
+        <v>31600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.67%</t>
+          <t>'+12.46%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.02</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="H6" t="n">
-        <v>2.85</v>
+        <v>11.44</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5880</v>
+        <v>28100</v>
       </c>
       <c r="K6" t="n">
-        <v>5950</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6920</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5840</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.83</v>
+        <v>11.46</v>
       </c>
       <c r="O6" t="n">
-        <v>91404224895</v>
+        <v>208195000000</v>
       </c>
       <c r="P6" t="n">
-        <v>11760</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>728000</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>박스권 돌파 및 전환사채 이슈. 외국인 순매수 1위 및 6500원 반등 가능성 언급.</t>
+          <t>가온전선과의 비교 속 저평가 해소 및 상승 기대. 36,000원 도달 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['박스권 돌파', '외국인 순매수', '전환사채']</t>
+          <t>['저평가', '가온전선', '상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12560</v>
+        <v>14040</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.46%</t>
+          <t>'+9.95%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="F7" t="n">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>748</v>
+        <v>204</v>
       </c>
       <c r="H7" t="n">
-        <v>8.029999999999999</v>
+        <v>2.83</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,130 +1055,130 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11580</v>
+        <v>12770</v>
       </c>
       <c r="K7" t="n">
-        <v>12200</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>13820</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>12100</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>8.699999999999999</v>
+        <v>2.83</v>
       </c>
       <c r="O7" t="n">
-        <v>124764563080</v>
+        <v>148654000000</v>
       </c>
       <c r="P7" t="n">
-        <v>21150</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>8140</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>276000</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>169000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>서로 다른 의견 속 매도 후 셀그램 관련 뉴스 기대. 외인/기관 동시 매수 확인.</t>
+          <t>미국 LA 전력청 수주 가능성 제기 및 미주 매출 3.5배 증가. 제품 테스트 완료. 하지만 일부는 매도 의견 제시.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['셀그램', '외인', '기관']</t>
+          <t>['LA 전력청', '미주 매출', '수주 가능성']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13860</v>
+        <v>7995</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.78%</t>
+          <t>'+9.82%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="G8" t="n">
-        <v>205</v>
+        <v>420</v>
       </c>
       <c r="H8" t="n">
-        <v>2.83</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12860</v>
+        <v>7280</v>
       </c>
       <c r="K8" t="n">
-        <v>13020</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>14230</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.83</v>
+        <v>0.59</v>
       </c>
       <c r="O8" t="n">
-        <v>144717315340</v>
+        <v>156224000000</v>
       </c>
       <c r="P8" t="n">
-        <v>20300</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2885</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>130000</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 LA 전력청 수주 가능성 제기 및 미주 매출 3.5배 증가. 제품 테스트 완료. 하지만 일부는 매도 의견 제시.</t>
+          <t>공시 내용 기반 월요일 10,000원 돌파 기대감 있으나, 일부에서는 급락 및 폭포수 현상 우려.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['LA 전력청', '미주 매출', '수주 가능성']</t>
+          <t>['공시', '외국인 매수', '급락 우려']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1851000</v>
+        <v>12570</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+6.07%</t>
+          <t>'+9.21%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1</v>
+        <v>-0.67</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>185</v>
       </c>
       <c r="F9" t="n">
-        <v>460</v>
+        <v>104</v>
       </c>
       <c r="G9" t="n">
-        <v>2455</v>
+        <v>760</v>
       </c>
       <c r="H9" t="n">
-        <v>50.1</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1745000</v>
+        <v>11510</v>
       </c>
       <c r="K9" t="n">
-        <v>1810000</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1852000</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1805000</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>50.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>4347651510500</v>
+        <v>125769000000</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>333000</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>483000</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>116000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>연말 500만원 목표 및 쌍끌이 매수 확인. 자사주 체결 및 괴리율 언급.</t>
+          <t>서로 다른 의견 속 매도 후 셀그램 관련 뉴스 기대. 외인/기관 동시 매수 확인.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['목표가', '쌍끌이 매수', '자사주']</t>
+          <t>['셀그램', '외인', '기관']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13870</v>
+        <v>13840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.05%</t>
+          <t>'+7.20%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="H10" t="n">
         <v>4.92</v>
@@ -1331,34 +1331,34 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13330</v>
+        <v>12910</v>
       </c>
       <c r="K10" t="n">
-        <v>13600</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>14050</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>13210</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>4.99</v>
       </c>
       <c r="O10" t="n">
-        <v>70347148795</v>
+        <v>70893000000</v>
       </c>
       <c r="P10" t="n">
-        <v>30200</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3540</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>298000</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1391,123 +1391,123 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11010</v>
+        <v>4100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.77%</t>
+          <t>'+6.77%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E11" t="n">
-        <v>99</v>
+        <v>237</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="G11" t="n">
-        <v>220</v>
+        <v>877</v>
       </c>
       <c r="H11" t="n">
-        <v>12.5</v>
+        <v>0.55</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10610</v>
+        <v>3840</v>
       </c>
       <c r="K11" t="n">
-        <v>10730</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>12390</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>10510</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>12.6</v>
+        <v>0.95</v>
       </c>
       <c r="O11" t="n">
-        <v>117526979260</v>
+        <v>40359000000</v>
       </c>
       <c r="P11" t="n">
-        <v>14350</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>74000</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
+          <t>STO 사업 추진 및 미국 코인 거래 허용 호재 언급되나, 주포의 물량 넘김 및 공매도 패배, 나락행 우려 상존.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['호남 반도체', '기자회견', '국내 이익']</t>
+          <t>['STO', '코인 테마', '주포 물량']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10630</v>
+        <v>1849000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.71%</t>
+          <t>'+5.24%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.29</v>
+        <v>-0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>118</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>72</v>
+        <v>474</v>
       </c>
       <c r="G12" t="n">
-        <v>191</v>
+        <v>2564</v>
       </c>
       <c r="H12" t="n">
-        <v>18.13</v>
+        <v>50.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10250</v>
+        <v>1757000</v>
       </c>
       <c r="K12" t="n">
-        <v>10280</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>11500</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>10230</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>18.42</v>
+        <v>50.2</v>
       </c>
       <c r="O12" t="n">
-        <v>202530794275</v>
+        <v>4450323000000</v>
       </c>
       <c r="P12" t="n">
-        <v>22450</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1760</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-55000</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>긍정적/부정적 의견 혼재, 주가 하락 가능성 언급. 뚜렷한 근거 없이 감정적 상승 기대.</t>
+          <t>자사주 매입 체결 확인 및 185선 돌파 시 추가 상승 전망. 200만에서 400만으로 목표 주가 상향 조정에 대한 기대감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['자사주 매입', '목표 주가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>261750</v>
+        <v>52500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.66%</t>
+          <t>'+4.58%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>179</v>
       </c>
       <c r="F13" t="n">
-        <v>444</v>
+        <v>93</v>
       </c>
       <c r="G13" t="n">
-        <v>1894</v>
+        <v>513</v>
       </c>
       <c r="H13" t="n">
-        <v>46.48</v>
+        <v>38.54</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>252500</v>
+        <v>50200</v>
       </c>
       <c r="K13" t="n">
-        <v>261000</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>262000</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>257500</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>46.52</v>
+        <v>38.62</v>
       </c>
       <c r="O13" t="n">
-        <v>2446660525250</v>
+        <v>242183000000</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>78600</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-1533000</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>874000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대통령 및 정치 관련 언급이 주를 이루며, 기자회견 내용에 대한 부정적 평가.</t>
+          <t>기관 및 외인 매수세 유입 속 개인 매도세 관찰. 4분기 수주 예상액 기반 우상향 전망 및 10만 전자 기대감 표출.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['기자회견', '정치', '검찰개혁']</t>
+          <t>['수주', '외인 매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19000</v>
+        <v>261250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.76%</t>
+          <t>'+3.06%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>158</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>79</v>
+        <v>443</v>
       </c>
       <c r="G14" t="n">
-        <v>468</v>
+        <v>1911</v>
       </c>
       <c r="H14" t="n">
-        <v>10.74</v>
+        <v>46.48</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18490</v>
+        <v>253500</v>
       </c>
       <c r="K14" t="n">
-        <v>18900</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>19700</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>18760</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>10.85</v>
+        <v>46.52</v>
       </c>
       <c r="O14" t="n">
-        <v>128642986280</v>
+        <v>2531364000000</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>135000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 원전주 상승 및 중동 전쟁 이슈 속 대차 해지 운동 주장. 수주 발표 후 하락에 대한 의문 제기.</t>
+          <t>주가 관련 내용 없이 정치 관련 이슈에 대한 부정적이고 감정적인 의견만 게시됨.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전주', '대차해지', '수주']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52500</v>
+        <v>86400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.74%</t>
+          <t>'+2.73%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>177</v>
+        <v>292</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>157</v>
       </c>
       <c r="G15" t="n">
-        <v>494</v>
+        <v>1314</v>
       </c>
       <c r="H15" t="n">
-        <v>38.54</v>
+        <v>23.23</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>51100</v>
+        <v>84100</v>
       </c>
       <c r="K15" t="n">
-        <v>51600</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>55200</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>51500</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>38.62</v>
+        <v>23.27</v>
       </c>
       <c r="O15" t="n">
-        <v>239231079900</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>67300</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>23150</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>447000</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>252000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성E&amp;A의 주가 상승 기대감과 외인/기관 매수세 언급. 세금 정책 관련 언급 있으나 주가와 직접적 연관성 부족.</t>
+          <t>뉴욕 원전주 급등 및 미국 투자 관련 발표 가능성. 웨스팅하우스 관련 리스크 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['삼성E&amp;A', '외인', '기관']</t>
+          <t>['원전주', '미국 투자', '웨스팅하우스']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17560</v>
+        <v>17540</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.80%</t>
+          <t>'+2.45%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1883,31 +1883,31 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17250</v>
+        <v>17120</v>
       </c>
       <c r="K16" t="n">
-        <v>17920</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>18440</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>17450</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>84538546555</v>
+        <v>85166000000</v>
       </c>
       <c r="P16" t="n">
-        <v>30550</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-97000</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1943,60 +1943,60 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4160</v>
+        <v>19050</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.59%</t>
+          <t>'+2.36%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="E17" t="n">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="F17" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="G17" t="n">
-        <v>207</v>
+        <v>469</v>
       </c>
       <c r="H17" t="n">
-        <v>0.73</v>
+        <v>10.74</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4095</v>
+        <v>18610</v>
       </c>
       <c r="K17" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>4400</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4095</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.87</v>
+        <v>10.85</v>
       </c>
       <c r="O17" t="n">
-        <v>70640387036</v>
+        <v>129919000000</v>
       </c>
       <c r="P17" t="n">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2006,60 +2006,60 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
+          <t>미국 원전주 상승 및 중동 전쟁 이슈 속 대차 해지 운동 주장. 수주 발표 후 하락에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
+          <t>['원전주', '대차해지', '수주']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13370</v>
+        <v>10570</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'-0.19%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0.29</v>
       </c>
       <c r="E18" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F18" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G18" t="n">
-        <v>395</v>
+        <v>196</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>18.13</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,91 +2067,91 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13360</v>
+        <v>10590</v>
       </c>
       <c r="K18" t="n">
-        <v>13450</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>14450</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>13280</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>18.42</v>
       </c>
       <c r="O18" t="n">
-        <v>41864271890</v>
+        <v>205644000000</v>
       </c>
       <c r="P18" t="n">
-        <v>19380</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-88000</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 상승 및 호남 반도체 사업 재개 기대감과 동시에, 단기 급등 후 하락 가능성 및 매도 의견 상존.</t>
+          <t>종목명 '광전자'에 대한 긍정적 기대와 함께 주가 조작 가능성 및 급락 가능성도 언급. 단기 등락에 대한 기대감과 우려가 혼재.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['호남 반도체', '실적', '단기 급등']</t>
+          <t>['주가 조작', '등락']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>85200</v>
+        <v>10100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.23%</t>
+          <t>'-0.49%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>286</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
-        <v>154</v>
+        <v>40</v>
       </c>
       <c r="G19" t="n">
-        <v>1305</v>
+        <v>227</v>
       </c>
       <c r="H19" t="n">
-        <v>23.23</v>
+        <v>1.24</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,183 +2159,183 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>85400</v>
+        <v>10150</v>
       </c>
       <c r="K19" t="n">
-        <v>87300</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>87800</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>85100</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>23.27</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>121158467150</v>
+        <v>34701000000</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-476000</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-94000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>뉴욕 원전주 급등 및 미국 투자 관련 발표 가능성. 웨스팅하우스 관련 리스크 언급.</t>
+          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전주', '미국 투자', '웨스팅하우스']</t>
+          <t>['미프진', '재료소멸', '하한가']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17800</v>
+        <v>10940</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.73%</t>
+          <t>'-1.26%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.38</v>
+        <v>-0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>169</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="G20" t="n">
-        <v>401</v>
+        <v>225</v>
       </c>
       <c r="H20" t="n">
-        <v>0.98</v>
+        <v>12.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>17930</v>
+        <v>11080</v>
       </c>
       <c r="K20" t="n">
-        <v>18400</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>20400</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>17260</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6</v>
+        <v>12.6</v>
       </c>
       <c r="O20" t="n">
-        <v>83778068960</v>
+        <v>117942000000</v>
       </c>
       <c r="P20" t="n">
-        <v>21100</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9900</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>43000</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>단타 위주 매매 및 락업 해제 관련 언급. 주포의 움직임 및 엑시트 물량 소화 중.</t>
+          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['단타', '락업해제', '주포']</t>
+          <t>['호남 반도체', '기자회견', '국내 이익']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10110</v>
+        <v>13410</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-3.71%</t>
+          <t>'-2.40%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="G21" t="n">
-        <v>220</v>
+        <v>410</v>
       </c>
       <c r="H21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>10500</v>
+        <v>13740</v>
       </c>
       <c r="K21" t="n">
-        <v>10650</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>10710</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>10100</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>34409387165</v>
+        <v>41982000000</v>
       </c>
       <c r="P21" t="n">
-        <v>15960</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-114000</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
+          <t>실적 상승 및 호남 반도체 사업 재개 기대감과 동시에, 단기 급등 후 하락 가능성 및 매도 의견 상존.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['미프진', '재료소멸', '하한가']</t>
+          <t>['호남 반도체', '실적', '단기 급등']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4120</v>
+        <v>4135</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-11.11%</t>
+          <t>'-6.55%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.4</v>
+        <v>-0.14</v>
       </c>
       <c r="E22" t="n">
-        <v>229</v>
+        <v>90</v>
       </c>
       <c r="F22" t="n">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="G22" t="n">
-        <v>863</v>
+        <v>207</v>
       </c>
       <c r="H22" t="n">
-        <v>0.55</v>
+        <v>0.73</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,60 +2435,60 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>4635</v>
+        <v>4425</v>
       </c>
       <c r="K22" t="n">
-        <v>4465</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>4535</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4065</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="O22" t="n">
-        <v>39407894761</v>
+        <v>71574000000</v>
       </c>
       <c r="P22" t="n">
-        <v>6900</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1738</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-108000</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>STO 사업 추진 및 미국 코인 거래 허용 호재 언급되나, 주포의 물량 넘김 및 공매도 패배, 나락행 우려 상존.</t>
+          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['STO', '코인 테마', '주포 물량']</t>
+          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -2503,17 +2503,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-53.49%</t>
+          <t>'-64.29%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.02</v>
       </c>
       <c r="E23" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G23" t="n">
         <v>143</v>
@@ -2527,31 +2527,31 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="K23" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>3.71</v>
       </c>
       <c r="O23" t="n">
-        <v>186468105</v>
+        <v>203000000</v>
       </c>
       <c r="P23" t="n">
-        <v>901</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-58000</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>

--- a/data/trending_integrated_20260918_14.xlsx
+++ b/data/trending_integrated_20260918_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26250</v>
+        <v>26500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+39.04%</t>
+          <t>'+22.69%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F2" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G2" t="n">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>18880</v>
+        <v>21600</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>22250</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>28050</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>21700</v>
       </c>
       <c r="N2" t="n">
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>435261000000</v>
+        <v>441803686800</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>59600</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-213000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>181000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>강력한 매수세와 함께 5~6만원대 재진입 신호 및 미래 SK하이닉스와 같은 성장성 언급. 45% 수익 달성.</t>
+          <t>업황 및 실적 성장성에 기반한 강한 상승세와 폭풍 매수 관찰.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['매수세', '성장성']</t>
+          <t>['성장성', '실적', '매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17930</v>
+        <v>18470</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.73%</t>
+          <t>'+14.51%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.38</v>
+        <v>-0.27</v>
       </c>
       <c r="E3" t="n">
-        <v>173</v>
+        <v>466</v>
       </c>
       <c r="F3" t="n">
-        <v>75</v>
+        <v>275</v>
       </c>
       <c r="G3" t="n">
-        <v>400</v>
+        <v>2613</v>
       </c>
       <c r="H3" t="n">
-        <v>0.98</v>
+        <v>4.61</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>15360</v>
+        <v>16130</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>16360</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>18990</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>16170</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6</v>
+        <v>4.88</v>
       </c>
       <c r="O3" t="n">
-        <v>84670000000</v>
+        <v>836985837510</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1369000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>147000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>단타 위주 매매 및 락업 해제 관련 언급. 주포의 움직임 및 엑시트 물량 소화 중.</t>
+          <t>대한광통신의 급등세 및 2차 매물대 돌파에 대한 기대감. 미국 증시 관련 뉴스 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['단타', '락업해제', '주포']</t>
+          <t>['대한광통신', '매물대', '공매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6470</v>
+        <v>7970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.12%</t>
+          <t>'+13.53%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.02</v>
+        <v>0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>207</v>
+        <v>427</v>
       </c>
       <c r="H4" t="n">
-        <v>2.85</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5620</v>
+        <v>7020</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>7180</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>8890</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>7150</v>
       </c>
       <c r="N4" t="n">
-        <v>1.83</v>
+        <v>0.59</v>
       </c>
       <c r="O4" t="n">
-        <v>92275000000</v>
+        <v>157195067495</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1206</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>627000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>26년말 매출액 및 영업이익 예상치 기반 긍정적 전망. 전환사채 발행에도 상한가 기대감 및 외국인 대규모 매수세 분석.</t>
+          <t>공시 내용 기반 월요일 10,000원 돌파 기대감 있으나, 일부에서는 급락 및 폭포수 현상 우려.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['매출액', '영업이익', '외국인 매수']</t>
+          <t>['공시', '외국인 매수', '급락 우려']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,95 +827,95 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18450</v>
+        <v>31750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.68%</t>
+          <t>'+12.19%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.27</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>458</v>
+        <v>148</v>
       </c>
       <c r="F5" t="n">
-        <v>273</v>
+        <v>73</v>
       </c>
       <c r="G5" t="n">
-        <v>2590</v>
+        <v>250</v>
       </c>
       <c r="H5" t="n">
-        <v>4.61</v>
+        <v>11.44</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16230</v>
+        <v>28300</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>28850</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>32050</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>28550</v>
       </c>
       <c r="N5" t="n">
-        <v>4.88</v>
+        <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>828470000000</v>
+        <v>219048299850</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>75900</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>249000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대한광통신의 급등세 및 2차 매물대 돌파에 대한 기대감. 미국 증시 관련 뉴스 및 공매도 관련 언급.</t>
+          <t>가온전선과의 비교 속 저평가 해소 및 박스권 탈출 시도.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['대한광통신', '매물대', '공매도']</t>
+          <t>['저평가', '박스권', '가온전선']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,86 +924,86 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31600</v>
+        <v>6440</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.46%</t>
+          <t>'+9.52%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="H6" t="n">
-        <v>11.44</v>
+        <v>2.85</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>28100</v>
+        <v>5880</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>6920</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5840</v>
       </c>
       <c r="N6" t="n">
-        <v>11.46</v>
+        <v>1.83</v>
       </c>
       <c r="O6" t="n">
-        <v>208195000000</v>
+        <v>93245838685</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>11760</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>728000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 속 저평가 해소 및 상승 기대. 36,000원 도달 가능성 언급.</t>
+          <t>26년말 매출액 및 영업이익 예상치 기반 긍정적 전망. 전환사채 발행에도 상한가 기대감 및 외국인 대규모 매수세 분석.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저평가', '가온전선', '상승']</t>
+          <t>['매출액', '영업이익', '외국인 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
@@ -1031,20 +1031,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.95%</t>
+          <t>'+9.18%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F7" t="n">
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H7" t="n">
         <v>2.83</v>
@@ -1055,34 +1055,34 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>12770</v>
+        <v>12860</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>13020</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>14230</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="N7" t="n">
         <v>2.83</v>
       </c>
       <c r="O7" t="n">
-        <v>148654000000</v>
+        <v>152585144545</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>20300</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2885</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1115,123 +1115,123 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7995</v>
+        <v>12540</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.82%</t>
+          <t>'+8.29%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1</v>
+        <v>-0.67</v>
       </c>
       <c r="E8" t="n">
-        <v>108</v>
+        <v>185</v>
       </c>
       <c r="F8" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="G8" t="n">
-        <v>420</v>
+        <v>788</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6899999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7280</v>
+        <v>11580</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>12200</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>13820</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>12100</v>
       </c>
       <c r="N8" t="n">
-        <v>0.59</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>156224000000</v>
+        <v>126972660635</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>21150</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>8140</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>276000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>169000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>공시 내용 기반 월요일 10,000원 돌파 기대감 있으나, 일부에서는 급락 및 폭포수 현상 우려.</t>
+          <t>개인 투자자들의 손실 경험과 외인/기관 동시 매수에 대한 엇갈린 시각.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공시', '외국인 매수', '급락 우려']</t>
+          <t>['외인', '기관', '손실']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12570</v>
+        <v>1850000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+9.21%</t>
+          <t>'+6.02%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.67</v>
+        <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>104</v>
+        <v>475</v>
       </c>
       <c r="G9" t="n">
-        <v>760</v>
+        <v>2557</v>
       </c>
       <c r="H9" t="n">
-        <v>8.029999999999999</v>
+        <v>50.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11510</v>
+        <v>1745000</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1810000</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1852000</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1805000</v>
       </c>
       <c r="N9" t="n">
-        <v>8.699999999999999</v>
+        <v>50.2</v>
       </c>
       <c r="O9" t="n">
-        <v>125769000000</v>
+        <v>4585252259500</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>333000</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>483000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>116000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>서로 다른 의견 속 매도 후 셀그램 관련 뉴스 기대. 외인/기관 동시 매수 확인.</t>
+          <t>200만원 돌파 기대감과 자사주 매입, 기관/외인 쌍끌이 매수에 따른 우상향 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['셀그램', '외인', '기관']</t>
+          <t>['자사주', '외인', '기관']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13840</v>
+        <v>13880</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.20%</t>
+          <t>'+4.13%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="H10" t="n">
         <v>4.92</v>
@@ -1331,34 +1331,34 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>12910</v>
+        <v>13330</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>13600</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>14050</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>13210</v>
       </c>
       <c r="N10" t="n">
         <v>4.99</v>
       </c>
       <c r="O10" t="n">
-        <v>70893000000</v>
+        <v>71628771220</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>30200</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3540</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>298000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4100</v>
+        <v>261500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+6.77%</t>
+          <t>'+3.56%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.4</v>
+        <v>-0.04</v>
       </c>
       <c r="E11" t="n">
-        <v>237</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>134</v>
+        <v>442</v>
       </c>
       <c r="G11" t="n">
-        <v>877</v>
+        <v>1919</v>
       </c>
       <c r="H11" t="n">
-        <v>0.55</v>
+        <v>46.48</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3840</v>
+        <v>252500</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>262000</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>257500</v>
       </c>
       <c r="N11" t="n">
-        <v>0.95</v>
+        <v>46.52</v>
       </c>
       <c r="O11" t="n">
-        <v>40359000000</v>
+        <v>2622926197250</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>78600</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-1533000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>874000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>STO 사업 추진 및 미국 코인 거래 허용 호재 언급되나, 주포의 물량 넘김 및 공매도 패배, 나락행 우려 상존.</t>
+          <t>주가 관련 내용 없이 정치 관련 이슈에 대한 부정적이고 감정적인 의견만 게시됨.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['STO', '코인 테마', '주포 물량']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1849000</v>
+        <v>10590</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+5.24%</t>
+          <t>'+3.32%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.1</v>
+        <v>-0.29</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>124</v>
       </c>
       <c r="F12" t="n">
-        <v>474</v>
+        <v>74</v>
       </c>
       <c r="G12" t="n">
-        <v>2564</v>
+        <v>202</v>
       </c>
       <c r="H12" t="n">
-        <v>50.1</v>
+        <v>18.13</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1757000</v>
+        <v>10250</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>10280</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>11500</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>10230</v>
       </c>
       <c r="N12" t="n">
-        <v>50.2</v>
+        <v>18.42</v>
       </c>
       <c r="O12" t="n">
-        <v>4450323000000</v>
+        <v>207749486050</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>22450</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1760</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-55000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>자사주 매입 체결 확인 및 185선 돌파 시 추가 상승 전망. 200만에서 400만으로 목표 주가 상향 조정에 대한 기대감.</t>
+          <t>주가 조작 의혹 및 20% 상승 기대감과 8천원대 하락 전망 혼재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['자사주 매입', '목표 주가']</t>
+          <t>['주가 조작', '외인', '거래량']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52500</v>
+        <v>10960</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+4.58%</t>
+          <t>'+3.30%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="F13" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="H13" t="n">
-        <v>38.54</v>
+        <v>12.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>50200</v>
+        <v>10610</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>10730</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>12390</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>10510</v>
       </c>
       <c r="N13" t="n">
-        <v>38.62</v>
+        <v>12.6</v>
       </c>
       <c r="O13" t="n">
-        <v>242183000000</v>
+        <v>118175925600</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>14350</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>74000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>기관 및 외인 매수세 유입 속 개인 매도세 관찰. 4분기 수주 예상액 기반 우상향 전망 및 10만 전자 기대감 표출.</t>
+          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주', '외인 매수']</t>
+          <t>['호남 반도체', '기자회견', '국내 이익']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>261250</v>
+        <v>19060</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.06%</t>
+          <t>'+3.08%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.04</v>
+        <v>-0.11</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>159</v>
       </c>
       <c r="F14" t="n">
-        <v>443</v>
+        <v>79</v>
       </c>
       <c r="G14" t="n">
-        <v>1911</v>
+        <v>488</v>
       </c>
       <c r="H14" t="n">
-        <v>46.48</v>
+        <v>10.74</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>253500</v>
+        <v>18490</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>18900</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>19700</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>18760</v>
       </c>
       <c r="N14" t="n">
-        <v>46.52</v>
+        <v>10.85</v>
       </c>
       <c r="O14" t="n">
-        <v>2531364000000</v>
+        <v>131342727475</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>135000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 관련 내용 없이 정치 관련 이슈에 대한 부정적이고 감정적인 의견만 게시됨.</t>
+          <t>미국장 원전주 상승 및 중동 전쟁 관련 이슈 속 대차해지 운동.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['원전', '대차해지', '수주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86400</v>
+        <v>52300</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+2.35%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E15" t="n">
-        <v>292</v>
+        <v>181</v>
       </c>
       <c r="F15" t="n">
-        <v>157</v>
+        <v>93</v>
       </c>
       <c r="G15" t="n">
-        <v>1314</v>
+        <v>507</v>
       </c>
       <c r="H15" t="n">
-        <v>23.23</v>
+        <v>38.54</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>84100</v>
+        <v>51100</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>51600</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>55200</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>51500</v>
       </c>
       <c r="N15" t="n">
-        <v>23.27</v>
+        <v>38.62</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>244615153350</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>67300</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>23150</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>447000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>252000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>뉴욕 원전주 급등 및 미국 투자 관련 발표 가능성. 웨스팅하우스 관련 리스크 언급.</t>
+          <t>4분기 수주 예상액 기반 10만 전자 전망과 외인/기관 매수세.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전주', '미국 투자', '웨스팅하우스']</t>
+          <t>['수주', '외인', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17540</v>
+        <v>17560</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.45%</t>
+          <t>'+1.80%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.27</v>
       </c>
       <c r="E16" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F16" t="n">
         <v>54</v>
       </c>
       <c r="G16" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H16" t="n">
         <v>0.97</v>
@@ -1883,31 +1883,31 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17120</v>
+        <v>17250</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>17920</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>18440</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>17450</v>
       </c>
       <c r="N16" t="n">
         <v>0.7</v>
       </c>
       <c r="O16" t="n">
-        <v>85166000000</v>
+        <v>85583205450</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>30550</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-97000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1943,60 +1943,60 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19050</v>
+        <v>4135</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+2.36%</t>
+          <t>'+0.98%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="E17" t="n">
-        <v>158</v>
+        <v>92</v>
       </c>
       <c r="F17" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
-        <v>469</v>
+        <v>212</v>
       </c>
       <c r="H17" t="n">
-        <v>10.74</v>
+        <v>0.73</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>18610</v>
+        <v>4095</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4095</v>
       </c>
       <c r="N17" t="n">
-        <v>10.85</v>
+        <v>0.87</v>
       </c>
       <c r="O17" t="n">
-        <v>129919000000</v>
+        <v>72616270734</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2006,60 +2006,60 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 원전주 상승 및 중동 전쟁 이슈 속 대차 해지 운동 주장. 수주 발표 후 하락에 대한 의문 제기.</t>
+          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전주', '대차해지', '수주']</t>
+          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10570</v>
+        <v>13370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.19%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.29</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F18" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G18" t="n">
-        <v>196</v>
+        <v>417</v>
       </c>
       <c r="H18" t="n">
-        <v>18.13</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,183 +2067,183 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>10590</v>
+        <v>13360</v>
       </c>
       <c r="K18" t="n">
+        <v>13450</v>
+      </c>
+      <c r="L18" t="n">
+        <v>14450</v>
+      </c>
+      <c r="M18" t="n">
+        <v>13280</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>18.42</v>
-      </c>
       <c r="O18" t="n">
-        <v>205644000000</v>
+        <v>42219333970</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>19380</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-88000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>종목명 '광전자'에 대한 긍정적 기대와 함께 주가 조작 가능성 및 급락 가능성도 언급. 단기 등락에 대한 기대감과 우려가 혼재.</t>
+          <t>실적 상승 및 호남 반도체 사업 재개 기대감과 동시에, 단기 급등 후 하락 가능성 및 매도 의견 상존.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 조작', '등락']</t>
+          <t>['호남 반도체', '실적', '단기 급등']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10100</v>
+        <v>17940</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.49%</t>
+          <t>'+0.06%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.01</v>
+        <v>0.38</v>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>176</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="G19" t="n">
-        <v>227</v>
+        <v>414</v>
       </c>
       <c r="H19" t="n">
-        <v>1.24</v>
+        <v>0.98</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10150</v>
+        <v>17930</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>18400</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>17260</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>0.6</v>
       </c>
       <c r="O19" t="n">
-        <v>34701000000</v>
+        <v>85463079720</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>21100</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
+          <t>락업 해제 및 주포의 움직임에 대한 경계와 단기 매매 선호 의견.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['미프진', '재료소멸', '하한가']</t>
+          <t>['락업 해제', '주포', '매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10940</v>
+        <v>85400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-1.26%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>295</v>
       </c>
       <c r="F20" t="n">
-        <v>46</v>
+        <v>156</v>
       </c>
       <c r="G20" t="n">
-        <v>225</v>
+        <v>1344</v>
       </c>
       <c r="H20" t="n">
-        <v>12.5</v>
+        <v>23.23</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,91 +2251,91 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>11080</v>
+        <v>85400</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>87300</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>87800</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>85100</v>
       </c>
       <c r="N20" t="n">
-        <v>12.6</v>
+        <v>23.27</v>
       </c>
       <c r="O20" t="n">
-        <v>117942000000</v>
+        <v>125472342900</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>139200</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>-476000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-94000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
+          <t>미국 원전주 급등 및 한미 외교 장관 회담 관련 대미 투자 기대감.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['호남 반도체', '기자회견', '국내 이익']</t>
+          <t>['원전', '대미 투자', '수주']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13410</v>
+        <v>10040</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.40%</t>
+          <t>'-4.38%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="F21" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>410</v>
+        <v>229</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>13740</v>
+        <v>10500</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>10650</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>10710</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>10030</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>41982000000</v>
+        <v>36174491485</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>15960</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>-114000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>실적 상승 및 호남 반도체 사업 재개 기대감과 동시에, 단기 급등 후 하락 가능성 및 매도 의견 상존.</t>
+          <t>먹는 임신중지약(미프진) 도입 관련 이슈 소멸 우려 및 대통령 언급 가능성에 따른 하한가 공포 확산. 프로그램 매수/매도 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['호남 반도체', '실적', '단기 급등']</t>
+          <t>['미프진', '재료소멸', '하한가']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4135</v>
+        <v>4095</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-6.55%</t>
+          <t>'-11.65%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.14</v>
+        <v>-0.4</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>237</v>
       </c>
       <c r="F22" t="n">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="G22" t="n">
-        <v>207</v>
+        <v>887</v>
       </c>
       <c r="H22" t="n">
-        <v>0.73</v>
+        <v>0.55</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,60 +2435,60 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>4425</v>
+        <v>4635</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>4465</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4535</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4065</v>
       </c>
       <c r="N22" t="n">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="O22" t="n">
-        <v>71574000000</v>
+        <v>40785918928</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1738</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>-108000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
+          <t>STO 사업 추진 및 미국 코인 거래 허용 호재 언급되나, 주포의 물량 넘김 및 공매도 패배, 나락행 우려 상존.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
+          <t>['STO', '코인 테마', '주포 물량']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -2503,20 +2503,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-64.29%</t>
+          <t>'-53.49%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.02</v>
       </c>
       <c r="E23" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H23" t="n">
         <v>3.69</v>
@@ -2527,31 +2527,31 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N23" t="n">
         <v>3.71</v>
       </c>
       <c r="O23" t="n">
-        <v>203000000</v>
+        <v>203077165</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>901</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>-58000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>

--- a/data/trending_integrated_20260918_14.xlsx
+++ b/data/trending_integrated_20260918_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26500</v>
+        <v>26700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.69%</t>
+          <t>'+23.61%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F2" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G2" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>441803686800</v>
+        <v>451509454125</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18470</v>
+        <v>7990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.51%</t>
+          <t>'+13.82%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.27</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>466</v>
+        <v>109</v>
       </c>
       <c r="F3" t="n">
-        <v>275</v>
+        <v>75</v>
       </c>
       <c r="G3" t="n">
-        <v>2613</v>
+        <v>431</v>
       </c>
       <c r="H3" t="n">
-        <v>4.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,91 +687,91 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16130</v>
+        <v>7020</v>
       </c>
       <c r="K3" t="n">
-        <v>16360</v>
+        <v>7180</v>
       </c>
       <c r="L3" t="n">
-        <v>18990</v>
+        <v>8890</v>
       </c>
       <c r="M3" t="n">
-        <v>16170</v>
+        <v>7150</v>
       </c>
       <c r="N3" t="n">
-        <v>4.88</v>
+        <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>836985837510</v>
+        <v>159043066230</v>
       </c>
       <c r="P3" t="n">
-        <v>31500</v>
+        <v>16200</v>
       </c>
       <c r="Q3" t="n">
-        <v>1272</v>
+        <v>1206</v>
       </c>
       <c r="R3" t="n">
-        <v>1369000</v>
+        <v>627000</v>
       </c>
       <c r="S3" t="n">
-        <v>147000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>대한광통신의 급등세 및 2차 매물대 돌파에 대한 기대감. 미국 증시 관련 뉴스 및 공매도 관련 언급.</t>
+          <t>공시 내용 기반 월요일 10,000원 돌파 기대감 있으나, 일부에서는 급락 및 폭포수 현상 우려.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['대한광통신', '매물대', '공매도']</t>
+          <t>['공시', '외국인 매수', '급락 우려']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>우리로</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7970</v>
+        <v>18090</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.53%</t>
+          <t>'+12.15%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>108</v>
+        <v>477</v>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>279</v>
       </c>
       <c r="G4" t="n">
-        <v>427</v>
+        <v>2645</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6899999999999999</v>
+        <v>4.61</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,60 +779,60 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7020</v>
+        <v>16130</v>
       </c>
       <c r="K4" t="n">
-        <v>7180</v>
+        <v>16360</v>
       </c>
       <c r="L4" t="n">
-        <v>8890</v>
+        <v>18990</v>
       </c>
       <c r="M4" t="n">
-        <v>7150</v>
+        <v>16170</v>
       </c>
       <c r="N4" t="n">
-        <v>0.59</v>
+        <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>157195067495</v>
+        <v>856518941390</v>
       </c>
       <c r="P4" t="n">
-        <v>16200</v>
+        <v>31500</v>
       </c>
       <c r="Q4" t="n">
-        <v>1206</v>
+        <v>1272</v>
       </c>
       <c r="R4" t="n">
-        <v>627000</v>
+        <v>1369000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>147000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>공시 내용 기반 월요일 10,000원 돌파 기대감 있으나, 일부에서는 급락 및 폭포수 현상 우려.</t>
+          <t>대한광통신의 급등세 및 2차 매물대 돌파에 대한 기대감. 미국 증시 관련 뉴스 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공시', '외국인 매수', '급락 우려']</t>
+          <t>['대한광통신', '매물대', '공매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>046970</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31750</v>
+        <v>31400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.19%</t>
+          <t>'+10.95%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G5" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="H5" t="n">
         <v>11.44</v>
@@ -886,7 +886,7 @@
         <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>219048299850</v>
+        <v>225323584500</v>
       </c>
       <c r="P5" t="n">
         <v>75900</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 속 저평가 해소 및 박스권 탈출 시도.</t>
+          <t>가온전선과의 비교 및 저평가 해소 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['저평가', '박스권', '가온전선']</t>
+          <t>['가온전선', '저평가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6440</v>
+        <v>6400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.52%</t>
+          <t>'+8.84%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H6" t="n">
         <v>2.85</v>
@@ -978,7 +978,7 @@
         <v>1.83</v>
       </c>
       <c r="O6" t="n">
-        <v>93245838685</v>
+        <v>93724489475</v>
       </c>
       <c r="P6" t="n">
         <v>11760</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>26년말 매출액 및 영업이익 예상치 기반 긍정적 전망. 전환사채 발행에도 상한가 기대감 및 외국인 대규모 매수세 분석.</t>
+          <t>전환사채 발행 및 박스권 돌파 기대, 외국인 투자자 매수.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['매출액', '영업이익', '외국인 매수']</t>
+          <t>['전환사채', '박스권 돌파', '외국인']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14040</v>
+        <v>12570</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.18%</t>
+          <t>'+8.55%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.67</v>
       </c>
       <c r="E7" t="n">
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="G7" t="n">
-        <v>208</v>
+        <v>792</v>
       </c>
       <c r="H7" t="n">
-        <v>2.83</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>12860</v>
+        <v>11580</v>
       </c>
       <c r="K7" t="n">
-        <v>13020</v>
+        <v>12200</v>
       </c>
       <c r="L7" t="n">
-        <v>14230</v>
+        <v>13820</v>
       </c>
       <c r="M7" t="n">
-        <v>13000</v>
+        <v>12100</v>
       </c>
       <c r="N7" t="n">
-        <v>2.83</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>152585144545</v>
+        <v>127767952780</v>
       </c>
       <c r="P7" t="n">
-        <v>20300</v>
+        <v>21150</v>
       </c>
       <c r="Q7" t="n">
-        <v>2885</v>
+        <v>8140</v>
       </c>
       <c r="R7" t="n">
-        <v>130000</v>
+        <v>276000</v>
       </c>
       <c r="S7" t="n">
-        <v>48000</v>
+        <v>169000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 LA 전력청 수주 가능성 제기 및 미주 매출 3.5배 증가. 제품 테스트 완료. 하지만 일부는 매도 의견 제시.</t>
+          <t>개인 투자자들의 손실 경험과 외인/기관 동시 매수에 대한 엇갈린 시각.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['LA 전력청', '미주 매출', '수주 가능성']</t>
+          <t>['외인', '기관', '손실']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12540</v>
+        <v>13910</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.29%</t>
+          <t>'+8.16%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>93</v>
       </c>
       <c r="F8" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="G8" t="n">
-        <v>788</v>
+        <v>215</v>
       </c>
       <c r="H8" t="n">
-        <v>8.029999999999999</v>
+        <v>2.83</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11580</v>
+        <v>12860</v>
       </c>
       <c r="K8" t="n">
-        <v>12200</v>
+        <v>13020</v>
       </c>
       <c r="L8" t="n">
-        <v>13820</v>
+        <v>14230</v>
       </c>
       <c r="M8" t="n">
-        <v>12100</v>
+        <v>13000</v>
       </c>
       <c r="N8" t="n">
-        <v>8.699999999999999</v>
+        <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>126972660635</v>
+        <v>154514926795</v>
       </c>
       <c r="P8" t="n">
-        <v>21150</v>
+        <v>20300</v>
       </c>
       <c r="Q8" t="n">
-        <v>8140</v>
+        <v>2885</v>
       </c>
       <c r="R8" t="n">
-        <v>276000</v>
+        <v>130000</v>
       </c>
       <c r="S8" t="n">
-        <v>169000</v>
+        <v>48000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>개인 투자자들의 손실 경험과 외인/기관 동시 매수에 대한 엇갈린 시각.</t>
+          <t>미국 LA 전력청 수주 가능성 제기 및 미주 매출 3.5배 증가. 제품 테스트 완료. 하지만 일부는 매도 의견 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외인', '기관', '손실']</t>
+          <t>['LA 전력청', '미주 매출', '수주 가능성']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1850000</v>
+        <v>1844000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+6.02%</t>
+          <t>'+5.67%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="G9" t="n">
-        <v>2557</v>
+        <v>2577</v>
       </c>
       <c r="H9" t="n">
         <v>50.1</v>
@@ -1254,7 +1254,7 @@
         <v>50.2</v>
       </c>
       <c r="O9" t="n">
-        <v>4585252259500</v>
+        <v>4691054493500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>200만원 돌파 기대감과 자사주 매입, 기관/외인 쌍끌이 매수에 따른 우상향 전망.</t>
+          <t>주가 상승 목표치 상향 조정 및 꾸준한 매수 의견.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['자사주', '외인', '기관']</t>
+          <t>['상승 목표', '매수', '자사주']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13880</v>
+        <v>13900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.13%</t>
+          <t>'+4.28%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F10" t="n">
         <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>617</v>
+        <v>627</v>
       </c>
       <c r="H10" t="n">
         <v>4.92</v>
@@ -1346,7 +1346,7 @@
         <v>4.99</v>
       </c>
       <c r="O10" t="n">
-        <v>71628771220</v>
+        <v>72714465595</v>
       </c>
       <c r="P10" t="n">
         <v>30200</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>261500</v>
+        <v>10950</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.56%</t>
+          <t>'+3.20%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>102</v>
       </c>
       <c r="F11" t="n">
-        <v>442</v>
+        <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>1919</v>
+        <v>224</v>
       </c>
       <c r="H11" t="n">
-        <v>46.48</v>
+        <v>12.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>252500</v>
+        <v>10610</v>
       </c>
       <c r="K11" t="n">
-        <v>261000</v>
+        <v>10730</v>
       </c>
       <c r="L11" t="n">
-        <v>262000</v>
+        <v>12390</v>
       </c>
       <c r="M11" t="n">
-        <v>257500</v>
+        <v>10510</v>
       </c>
       <c r="N11" t="n">
-        <v>46.52</v>
+        <v>12.6</v>
       </c>
       <c r="O11" t="n">
-        <v>2622926197250</v>
+        <v>118489726880</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>14350</v>
       </c>
       <c r="Q11" t="n">
-        <v>78600</v>
+        <v>465</v>
       </c>
       <c r="R11" t="n">
-        <v>-1533000</v>
+        <v>74000</v>
       </c>
       <c r="S11" t="n">
-        <v>874000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 관련 내용 없이 정치 관련 이슈에 대한 부정적이고 감정적인 의견만 게시됨.</t>
+          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,51 +1463,51 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['호남 반도체', '기자회견', '국내 이익']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>109</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10590</v>
+        <v>260500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.32%</t>
+          <t>'+3.17%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.29</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>124</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>74</v>
+        <v>438</v>
       </c>
       <c r="G12" t="n">
-        <v>202</v>
+        <v>1929</v>
       </c>
       <c r="H12" t="n">
-        <v>18.13</v>
+        <v>46.48</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10250</v>
+        <v>252500</v>
       </c>
       <c r="K12" t="n">
-        <v>10280</v>
+        <v>261000</v>
       </c>
       <c r="L12" t="n">
-        <v>11500</v>
+        <v>262000</v>
       </c>
       <c r="M12" t="n">
-        <v>10230</v>
+        <v>257500</v>
       </c>
       <c r="N12" t="n">
-        <v>18.42</v>
+        <v>46.52</v>
       </c>
       <c r="O12" t="n">
-        <v>207749486050</v>
+        <v>2681733144500</v>
       </c>
       <c r="P12" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>1760</v>
+        <v>78600</v>
       </c>
       <c r="R12" t="n">
-        <v>-55000</v>
+        <v>-1533000</v>
       </c>
       <c r="S12" t="n">
-        <v>1000</v>
+        <v>874000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 20% 상승 기대감과 8천원대 하락 전망 혼재.</t>
+          <t>정치 관련 기자회견 내용에 대한 비판.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가 조작', '외인', '거래량']</t>
+          <t>['기자회견', '정치']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10960</v>
+        <v>52450</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.30%</t>
+          <t>'+2.64%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E13" t="n">
-        <v>102</v>
+        <v>184</v>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="G13" t="n">
-        <v>228</v>
+        <v>518</v>
       </c>
       <c r="H13" t="n">
-        <v>12.5</v>
+        <v>38.54</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,60 +1607,60 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10610</v>
+        <v>51100</v>
       </c>
       <c r="K13" t="n">
-        <v>10730</v>
+        <v>51600</v>
       </c>
       <c r="L13" t="n">
-        <v>12390</v>
+        <v>55200</v>
       </c>
       <c r="M13" t="n">
-        <v>10510</v>
+        <v>51500</v>
       </c>
       <c r="N13" t="n">
-        <v>12.6</v>
+        <v>38.62</v>
       </c>
       <c r="O13" t="n">
-        <v>118175925600</v>
+        <v>250576597200</v>
       </c>
       <c r="P13" t="n">
-        <v>14350</v>
+        <v>67300</v>
       </c>
       <c r="Q13" t="n">
-        <v>465</v>
+        <v>23150</v>
       </c>
       <c r="R13" t="n">
-        <v>74000</v>
+        <v>447000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>252000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국내 이익 관련 기자회견 내용 및 호남 반도체 사업 추진 관련 불확실성에 대한 논의.</t>
+          <t>연말 수주 예상액 기반 긍정적 전망 및 우상향 추세 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['호남 반도체', '기자회견', '국내 이익']</t>
+          <t>['수주', '전망', '우상향']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19060</v>
+        <v>18940</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+3.08%</t>
+          <t>'+2.43%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.11</v>
       </c>
       <c r="E14" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F14" t="n">
         <v>79</v>
       </c>
       <c r="G14" t="n">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="H14" t="n">
         <v>10.74</v>
@@ -1714,7 +1714,7 @@
         <v>10.85</v>
       </c>
       <c r="O14" t="n">
-        <v>131342727475</v>
+        <v>133913324030</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국장 원전주 상승 및 중동 전쟁 관련 이슈 속 대차해지 운동.</t>
+          <t>대차해지 운동 동참 호소 및 중동 전쟁 관련 수혜 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '대차해지', '수주']</t>
+          <t>['대차해지', '중동 전쟁', '수주']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,123 +1759,123 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52300</v>
+        <v>17620</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.35%</t>
+          <t>'+2.14%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.08</v>
+        <v>0.27</v>
       </c>
       <c r="E15" t="n">
-        <v>181</v>
+        <v>101</v>
       </c>
       <c r="F15" t="n">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>507</v>
+        <v>195</v>
       </c>
       <c r="H15" t="n">
-        <v>38.54</v>
+        <v>0.97</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>51100</v>
+        <v>17250</v>
       </c>
       <c r="K15" t="n">
-        <v>51600</v>
+        <v>17920</v>
       </c>
       <c r="L15" t="n">
-        <v>55200</v>
+        <v>18440</v>
       </c>
       <c r="M15" t="n">
-        <v>51500</v>
+        <v>17450</v>
       </c>
       <c r="N15" t="n">
-        <v>38.62</v>
+        <v>0.7</v>
       </c>
       <c r="O15" t="n">
-        <v>244615153350</v>
+        <v>86602578135</v>
       </c>
       <c r="P15" t="n">
-        <v>67300</v>
+        <v>30550</v>
       </c>
       <c r="Q15" t="n">
-        <v>23150</v>
+        <v>6100</v>
       </c>
       <c r="R15" t="n">
-        <v>447000</v>
+        <v>-97000</v>
       </c>
       <c r="S15" t="n">
-        <v>252000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>4분기 수주 예상액 기반 10만 전자 전망과 외인/기관 매수세.</t>
+          <t>미국 양자컴퓨터 주식(아이온큐)의 급등에 따른 기대감이 형성되었으나, 국내 시장에서의 주가 변동성은 크며 양자컴퓨터, AI 반도체, 보안 관련주 내에서의 상대적 위치에 대한 논의가 있음. 공공기관 보안 이슈가 언급되나, 투자자 유입은 제한적이라는 의견도 존재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['수주', '외인', '공매도']</t>
+          <t>['양자컴퓨터', '보안', 'AI 반도체']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17560</v>
+        <v>4130</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.80%</t>
+          <t>'+0.85%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.27</v>
+        <v>-0.14</v>
       </c>
       <c r="E16" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G16" t="n">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="H16" t="n">
-        <v>0.97</v>
+        <v>0.73</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17250</v>
+        <v>4095</v>
       </c>
       <c r="K16" t="n">
-        <v>17920</v>
+        <v>4200</v>
       </c>
       <c r="L16" t="n">
-        <v>18440</v>
+        <v>4400</v>
       </c>
       <c r="M16" t="n">
-        <v>17450</v>
+        <v>4095</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7</v>
+        <v>0.87</v>
       </c>
       <c r="O16" t="n">
-        <v>85583205450</v>
+        <v>73553420106</v>
       </c>
       <c r="P16" t="n">
-        <v>30550</v>
+        <v>8100</v>
       </c>
       <c r="Q16" t="n">
-        <v>6100</v>
+        <v>592</v>
       </c>
       <c r="R16" t="n">
-        <v>-97000</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 양자컴퓨터 주식(아이온큐)의 급등에 따른 기대감이 형성되었으나, 국내 시장에서의 주가 변동성은 크며 양자컴퓨터, AI 반도체, 보안 관련주 내에서의 상대적 위치에 대한 논의가 있음. 공공기관 보안 이슈가 언급되나, 투자자 유입은 제한적이라는 의견도 존재.</t>
+          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '보안', 'AI 반도체']</t>
+          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4135</v>
+        <v>18000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.98%</t>
+          <t>'+0.39%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.14</v>
+        <v>0.38</v>
       </c>
       <c r="E17" t="n">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G17" t="n">
-        <v>212</v>
+        <v>419</v>
       </c>
       <c r="H17" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,60 +1975,60 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4095</v>
+        <v>17930</v>
       </c>
       <c r="K17" t="n">
-        <v>4200</v>
+        <v>18400</v>
       </c>
       <c r="L17" t="n">
-        <v>4400</v>
+        <v>20400</v>
       </c>
       <c r="M17" t="n">
-        <v>4095</v>
+        <v>17260</v>
       </c>
       <c r="N17" t="n">
-        <v>0.87</v>
+        <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>72616270734</v>
+        <v>86117488035</v>
       </c>
       <c r="P17" t="n">
-        <v>8100</v>
+        <v>21100</v>
       </c>
       <c r="Q17" t="n">
-        <v>592</v>
+        <v>9900</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 부양 노력 의지 언급 및 미국 광통신 시장 동향 기반 상승 기대감과 함께, 투기/투기과열 제도에 대한 불만 표출.</t>
+          <t>락업 해제 및 주포의 움직임에 대한 경계와 단기 매매 선호 의견.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['미국 광통신', '주가 부양', '투기/투기과열']</t>
+          <t>['락업 해제', '주포', '매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13370</v>
+        <v>13360</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F18" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G18" t="n">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>42219333970</v>
+        <v>42449959210</v>
       </c>
       <c r="P18" t="n">
         <v>19380</v>
@@ -2127,83 +2127,83 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17940</v>
+        <v>85350</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.06%</t>
+          <t>'-0.06%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.38</v>
+        <v>-0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>176</v>
+        <v>304</v>
       </c>
       <c r="F19" t="n">
-        <v>76</v>
+        <v>162</v>
       </c>
       <c r="G19" t="n">
-        <v>414</v>
+        <v>1340</v>
       </c>
       <c r="H19" t="n">
-        <v>0.98</v>
+        <v>23.23</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>17930</v>
+        <v>85400</v>
       </c>
       <c r="K19" t="n">
-        <v>18400</v>
+        <v>87300</v>
       </c>
       <c r="L19" t="n">
-        <v>20400</v>
+        <v>87800</v>
       </c>
       <c r="M19" t="n">
-        <v>17260</v>
+        <v>85100</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6</v>
+        <v>23.27</v>
       </c>
       <c r="O19" t="n">
-        <v>85463079720</v>
+        <v>128795587100</v>
       </c>
       <c r="P19" t="n">
-        <v>21100</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>9900</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>43000</v>
+        <v>-476000</v>
       </c>
       <c r="S19" t="n">
-        <v>-1000</v>
+        <v>-94000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>락업 해제 및 주포의 움직임에 대한 경계와 단기 매매 선호 의견.</t>
+          <t>미국 원전주 급등 및 한미 외교 장관 회담 관련 대미 투자 기대감.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['락업 해제', '주포', '매도']</t>
+          <t>['원전', '대미 투자', '수주']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>85400</v>
+        <v>10520</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.66%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.04</v>
+        <v>-0.29</v>
       </c>
       <c r="E20" t="n">
-        <v>295</v>
+        <v>126</v>
       </c>
       <c r="F20" t="n">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="G20" t="n">
-        <v>1344</v>
+        <v>212</v>
       </c>
       <c r="H20" t="n">
-        <v>23.23</v>
+        <v>18.13</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>85400</v>
+        <v>10590</v>
       </c>
       <c r="K20" t="n">
-        <v>87300</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>87800</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>85100</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>23.27</v>
+        <v>18.42</v>
       </c>
       <c r="O20" t="n">
-        <v>125472342900</v>
+        <v>209361000000</v>
       </c>
       <c r="P20" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-476000</v>
+        <v>-55000</v>
       </c>
       <c r="S20" t="n">
-        <v>-94000</v>
+        <v>1000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 한미 외교 장관 회담 관련 대미 투자 기대감.</t>
+          <t>주가 조작 의혹 제기 및 보유 물량 매도 의견.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '대미 투자', '수주']</t>
+          <t>['주가 조작', '매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10040</v>
+        <v>10110</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-4.38%</t>
+          <t>'-3.71%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2358,7 +2358,7 @@
         <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>36174491485</v>
+        <v>36484600205</v>
       </c>
       <c r="P21" t="n">
         <v>15960</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4095</v>
+        <v>4075</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-11.65%</t>
+          <t>'-12.08%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.4</v>
       </c>
       <c r="E22" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F22" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G22" t="n">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="H22" t="n">
         <v>0.55</v>
@@ -2450,7 +2450,7 @@
         <v>0.95</v>
       </c>
       <c r="O22" t="n">
-        <v>40785918928</v>
+        <v>41487692774</v>
       </c>
       <c r="P22" t="n">
         <v>6900</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>STO 사업 추진 및 미국 코인 거래 허용 호재 언급되나, 주포의 물량 넘김 및 공매도 패배, 나락행 우려 상존.</t>
+          <t>STO 사업 추진 및 미국 코인 관련 호재, 매수 기회.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['STO', '코인 테마', '주포 물량']</t>
+          <t>['STO', '코인', '호재']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2510,13 +2510,13 @@
         <v>-0.02</v>
       </c>
       <c r="E23" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G23" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H23" t="n">
         <v>3.69</v>
